--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7C333E-AD05-4F2E-AA5E-2495308BF43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FCC215-460F-407D-9525-6D801FE72BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="31">
   <si>
     <t>업무일자</t>
   </si>
@@ -532,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1423,6 +1423,196 @@
         <v>35</v>
       </c>
     </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1">
+        <v>46099.360983796294</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="1">
+        <v>46099.360983796294</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="1">
+        <v>46099.360983796294</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>25</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1">
+        <v>46099.360983796294</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="1">
+        <v>46099.360983796294</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FCC215-460F-407D-9525-6D801FE72BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F885ADC6-C4BF-4C6C-8368-1DE03B45C9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
   <si>
     <t>업무일자</t>
   </si>
@@ -47,28 +47,7 @@
     <t>작성일시</t>
   </si>
   <si>
-    <t>에디션 헤드레스트</t>
-  </si>
-  <si>
-    <t>L6 헤드레스트</t>
-  </si>
-  <si>
-    <t>네오 헤드레스트</t>
-  </si>
-  <si>
-    <t>SPQ 헤드레스트</t>
-  </si>
-  <si>
-    <t>오전업무</t>
-  </si>
-  <si>
-    <t>오후업무</t>
-  </si>
-  <si>
     <t>특이사항</t>
-  </si>
-  <si>
-    <t>코멘트</t>
   </si>
   <si>
     <t>홍숙란</t>
@@ -92,14 +71,6 @@
   </si>
   <si>
     <t>윤미애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리시트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리백커버</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -155,12 +126,82 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>입고수량</t>
+  </si>
+  <si>
+    <t>출고수량</t>
+  </si>
+  <si>
+    <t>반품수량</t>
+  </si>
+  <si>
+    <t>재고확인사항</t>
+  </si>
+  <si>
+    <t>배송이슈</t>
+  </si>
+  <si>
+    <t>오전 업무내용</t>
+  </si>
+  <si>
+    <t>오후 업무내용</t>
+  </si>
+  <si>
+    <t>미처리내역</t>
+  </si>
+  <si>
+    <t>예정사항</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>SPQ 수량</t>
+  </si>
+  <si>
+    <t>L6 수량</t>
+  </si>
+  <si>
+    <t>에디션 수량</t>
+  </si>
+  <si>
+    <t>네오 수량</t>
+  </si>
+  <si>
+    <t>네오패드</t>
+  </si>
+  <si>
+    <t>팰리 1열 7인</t>
+  </si>
+  <si>
+    <t>팰리 1열 9인</t>
+  </si>
+  <si>
     <t>포르쉐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>테슬라</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전용 1열</t>
+  </si>
+  <si>
+    <t>전용 2열</t>
+  </si>
+  <si>
+    <t>프리슬림</t>
+  </si>
+  <si>
+    <t>프리백</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>권주환</t>
+  </si>
+  <si>
+    <t>테스트</t>
   </si>
 </sst>
 </file>
@@ -203,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -229,6 +270,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,13 +576,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="8" width="25.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -550,7 +594,7 @@
     <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,55 +604,91 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="68" x14ac:dyDescent="0.45">
+      <c r="Q1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="68" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46094</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1">
         <v>46094.360983796294</v>
@@ -638,25 +718,25 @@
         <v>35</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46094</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>46094.360983796294</v>
@@ -683,15 +763,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="68" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" ht="68" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46094</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1">
         <v>46094.360983796294</v>
@@ -721,21 +801,21 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="85" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="85" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46094</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1">
         <v>46094.360983796294</v>
@@ -765,21 +845,21 @@
         <v>0</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46094</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1">
         <v>46094.360983796294</v>
@@ -809,21 +889,21 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46093</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1">
         <v>46093.360983796294</v>
@@ -853,15 +933,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46093</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1">
         <v>46093.360983796294</v>
@@ -891,15 +971,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46093</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1">
         <v>46093.360983796294</v>
@@ -929,15 +1009,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46093</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D10" s="1">
         <v>46093.360983796294</v>
@@ -967,15 +1047,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46093</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1">
         <v>46093.360983796294</v>
@@ -1005,15 +1085,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46097</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1">
         <v>46097.360983796294</v>
@@ -1043,15 +1123,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46097</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D13" s="1">
         <v>46097.360983796294</v>
@@ -1081,15 +1161,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>46097</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D14" s="1">
         <v>46097.360983796294</v>
@@ -1119,15 +1199,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46097</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1">
         <v>46097.360983796294</v>
@@ -1157,15 +1237,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46097</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1">
         <v>46097.360983796294</v>
@@ -1195,15 +1275,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46098</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1">
         <v>46098.360983796294</v>
@@ -1233,15 +1313,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46098</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1">
         <v>46098.360983796294</v>
@@ -1271,15 +1351,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46098</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D19" s="1">
         <v>46098.360983796294</v>
@@ -1309,15 +1389,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46098</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D20" s="1">
         <v>46098.360983796294</v>
@@ -1347,15 +1427,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46098</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1">
         <v>46098.360983796294</v>
@@ -1385,15 +1465,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46098</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1">
         <v>46098.360983796294</v>
@@ -1423,15 +1503,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46099</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D23" s="1">
         <v>46099.360983796294</v>
@@ -1461,15 +1541,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46099</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1">
         <v>46099.360983796294</v>
@@ -1499,15 +1579,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46099</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1">
         <v>46099.360983796294</v>
@@ -1537,15 +1617,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46099</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26" s="1">
         <v>46099.360983796294</v>
@@ -1575,15 +1655,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>46099</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D27" s="1">
         <v>46099.360983796294</v>
@@ -1611,6 +1691,59 @@
       </c>
       <c r="L27">
         <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="1">
+        <v>46107.072604166664</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>2</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>4</v>
+      </c>
+      <c r="T28">
+        <v>5</v>
+      </c>
+      <c r="U28">
+        <v>6</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>2</v>
+      </c>
+      <c r="Y28">
+        <v>4</v>
+      </c>
+      <c r="Z28">
+        <v>5</v>
+      </c>
+      <c r="AA28">
+        <v>3</v>
+      </c>
+      <c r="AB28">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645A5C52-32E0-4F3D-9E2F-43D81F53B185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F33E70-D017-403B-901A-9672581C49FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>업무일자</t>
   </si>
@@ -161,10 +161,6 @@
     <t>2026-03-31 08:35:59.708201</t>
   </si>
   <si>
-    <t>헤드하는중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2026-03-31 08:34:11.002186</t>
   </si>
   <si>
@@ -172,6 +168,27 @@
   </si>
   <si>
     <t>2026-03-31 04:08:20.969021</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-01 08:12:00.609874</t>
+  </si>
+  <si>
+    <t>새들.sp시작</t>
+  </si>
+  <si>
+    <t>2026-04-01 06:34:10.267148</t>
+  </si>
+  <si>
+    <t>2026-04-01 06:33:33.130845</t>
+  </si>
+  <si>
+    <t>2026-04-01 04:09:30.387897</t>
+  </si>
+  <si>
+    <t>헤드하는~중</t>
   </si>
 </sst>
 </file>
@@ -518,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.45">
@@ -609,7 +626,7 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
@@ -618,38 +635,38 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="Q2">
+        <v>35</v>
+      </c>
+      <c r="AB2">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3">
-        <v>4</v>
-      </c>
-      <c r="AA3">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -658,15 +675,15 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB4">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="X4">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
@@ -675,15 +692,15 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB5">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="Q5">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -692,18 +709,18 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
       </c>
       <c r="Y6">
-        <v>30</v>
-      </c>
-      <c r="AA6">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -712,50 +729,47 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y7">
-        <v>30</v>
-      </c>
-      <c r="Z7">
-        <v>10</v>
+        <v>42</v>
+      </c>
+      <c r="W7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="P8">
-        <v>18</v>
-      </c>
-      <c r="AA8">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="AB8">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA9">
-        <v>60</v>
+        <v>44</v>
+      </c>
+      <c r="AB9">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.45">
@@ -763,18 +777,95 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y10">
+        <v>30</v>
+      </c>
+      <c r="AA10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y11">
+        <v>30</v>
+      </c>
+      <c r="Z11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="P12">
+        <v>18</v>
+      </c>
+      <c r="AA12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="X10">
-        <v>30</v>
-      </c>
-      <c r="AA10">
+      <c r="X14">
+        <v>30</v>
+      </c>
+      <c r="AA14">
         <v>30</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F33E70-D017-403B-901A-9672581C49FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08EE714-E372-4264-8E17-821131FF178C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
   <si>
     <t>업무일자</t>
   </si>
@@ -189,6 +189,24 @@
   </si>
   <si>
     <t>헤드하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-02 23:59:41.079265</t>
+  </si>
+  <si>
+    <t>2026-04-02 08:34:57.504516</t>
+  </si>
+  <si>
+    <t>2026-04-02 06:32:21.958758</t>
+  </si>
+  <si>
+    <t>2026-04-02 06:30:45.742099</t>
+  </si>
+  <si>
+    <t>2026-04-02 03:53:33.774720</t>
   </si>
 </sst>
 </file>
@@ -535,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.45">
@@ -869,6 +887,106 @@
         <v>30</v>
       </c>
     </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="W16">
+        <v>11</v>
+      </c>
+      <c r="AB16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17">
+        <v>17</v>
+      </c>
+      <c r="AB17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="S18">
+        <v>12</v>
+      </c>
+      <c r="T18">
+        <v>24</v>
+      </c>
+      <c r="AB18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19">
+        <v>12</v>
+      </c>
+      <c r="AB19">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08EE714-E372-4264-8E17-821131FF178C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CFF465-845F-4552-B21E-AAC4FB156F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="64">
   <si>
     <t>업무일자</t>
   </si>
@@ -207,6 +207,24 @@
   </si>
   <si>
     <t>2026-04-02 03:53:33.774720</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-03 08:33:38.701839</t>
+  </si>
+  <si>
+    <t>2026-04-03 06:33:43.784936</t>
+  </si>
+  <si>
+    <t>2026-04-03 06:32:37.506259</t>
+  </si>
+  <si>
+    <t>2026-04-03 06:32:26.548555</t>
+  </si>
+  <si>
+    <t>2026-04-03 06:31:15.826363</t>
   </si>
 </sst>
 </file>
@@ -553,8 +571,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -985,6 +1026,97 @@
       </c>
       <c r="AB19">
         <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+      <c r="R20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21">
+        <v>35</v>
+      </c>
+      <c r="R21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="P22">
+        <v>35</v>
+      </c>
+      <c r="Q22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="P23">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>63</v>
+      </c>
+      <c r="R24">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CFF465-845F-4552-B21E-AAC4FB156F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCD0365-ED7E-414E-97E0-4E2F84A51DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="71">
   <si>
     <t>업무일자</t>
   </si>
@@ -225,6 +225,27 @@
   </si>
   <si>
     <t>2026-04-03 06:31:15.826363</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-06 08:42:18.845143</t>
+  </si>
+  <si>
+    <t>전용2열.옆날개하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-06 08:34:27.767037</t>
+  </si>
+  <si>
+    <t>2026-04-06 06:34:49.057741</t>
+  </si>
+  <si>
+    <t>2026-04-06 06:34:02.394096</t>
+  </si>
+  <si>
+    <t>2026-04-06 06:32:11.092761</t>
   </si>
 </sst>
 </file>
@@ -571,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -1119,6 +1140,115 @@
         <v>35</v>
       </c>
     </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" t="s">
+        <v>66</v>
+      </c>
+      <c r="R25">
+        <v>35</v>
+      </c>
+      <c r="AA25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+      <c r="P26">
+        <v>35</v>
+      </c>
+      <c r="AA26">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q27">
+        <v>35</v>
+      </c>
+      <c r="AA27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="P28">
+        <v>35</v>
+      </c>
+      <c r="AA28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+      <c r="P29">
+        <v>17</v>
+      </c>
+      <c r="Q29">
+        <v>18</v>
+      </c>
+      <c r="R29">
+        <v>17</v>
+      </c>
+      <c r="AB29">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\program\업무일지대시보드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCD0365-ED7E-414E-97E0-4E2F84A51DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE680C0-63B3-41B9-B95E-254BF6DDF46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="85">
   <si>
     <t>업무일자</t>
   </si>
@@ -95,12 +95,6 @@
     <t>네오패드</t>
   </si>
   <si>
-    <t>팰리 1열 7인</t>
-  </si>
-  <si>
-    <t>팰리 1열 9인</t>
-  </si>
-  <si>
     <t>포르쉐</t>
   </si>
   <si>
@@ -246,6 +240,54 @@
   </si>
   <si>
     <t>2026-04-06 06:32:11.092761</t>
+  </si>
+  <si>
+    <t>팰리 1열</t>
+  </si>
+  <si>
+    <t>팰리 2열_7인승</t>
+  </si>
+  <si>
+    <t>팰리 2열_9인승</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-08 22:34:41.319675</t>
+  </si>
+  <si>
+    <t>헤드.토프.하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-08 08:33:33.507552</t>
+  </si>
+  <si>
+    <t>2026-04-08 06:32:43.451983</t>
+  </si>
+  <si>
+    <t>2026-04-08 04:19:21.491385</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-07 08:33:14.313211</t>
+  </si>
+  <si>
+    <t>2026-04-07 06:35:55.051172</t>
+  </si>
+  <si>
+    <t>2026-04-07 06:34:34.263751</t>
+  </si>
+  <si>
+    <t>백커버.하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-07 06:33:38.198591</t>
+  </si>
+  <si>
+    <t>2026-04-07 04:10:50.737382</t>
   </si>
 </sst>
 </file>
@@ -592,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -612,13 +654,14 @@
     <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -680,572 +723,740 @@
         <v>19</v>
       </c>
       <c r="U1" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W1" t="s">
+        <v>71</v>
+      </c>
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2">
+        <v>35</v>
+      </c>
+      <c r="AC2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7">
+        <v>4</v>
+      </c>
+      <c r="AB7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q2">
-        <v>35</v>
-      </c>
-      <c r="AB2">
+      <c r="Z10">
+        <v>30</v>
+      </c>
+      <c r="AB10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z11">
+        <v>30</v>
+      </c>
+      <c r="AA11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q12">
+        <v>18</v>
+      </c>
+      <c r="AB12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y14">
+        <v>30</v>
+      </c>
+      <c r="AB14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="X16">
+        <v>11</v>
+      </c>
+      <c r="AC16">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB3">
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17">
+        <v>17</v>
+      </c>
+      <c r="AC17">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="T18">
+        <v>12</v>
+      </c>
+      <c r="U18">
+        <v>24</v>
+      </c>
+      <c r="AC18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="T19">
+        <v>12</v>
+      </c>
+      <c r="AC19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="S20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q21">
+        <v>35</v>
+      </c>
+      <c r="S21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q22">
+        <v>35</v>
+      </c>
+      <c r="R22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q23">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="W7">
-        <v>4</v>
-      </c>
-      <c r="AA7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="S24">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25">
+        <v>35</v>
+      </c>
+      <c r="AB25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q26">
+        <v>35</v>
+      </c>
+      <c r="AB26">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB8">
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+      <c r="R27">
+        <v>35</v>
+      </c>
+      <c r="AB27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q28">
+        <v>35</v>
+      </c>
+      <c r="AB28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q29">
+        <v>17</v>
+      </c>
+      <c r="R29">
+        <v>18</v>
+      </c>
+      <c r="S29">
+        <v>17</v>
+      </c>
+      <c r="AC29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC30">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB9">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB31">
+        <v>21</v>
+      </c>
+      <c r="AC31">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y10">
-        <v>30</v>
-      </c>
-      <c r="AA10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y11">
-        <v>30</v>
-      </c>
-      <c r="Z11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" t="s">
+        <v>76</v>
+      </c>
+      <c r="P32">
+        <v>35</v>
+      </c>
+      <c r="AC32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA34">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>81</v>
+      </c>
+      <c r="L36" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA36">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="P12">
-        <v>18</v>
-      </c>
-      <c r="AA12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB37">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="X14">
-        <v>30</v>
-      </c>
-      <c r="AA14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="P15">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>54</v>
-      </c>
-      <c r="W16">
-        <v>11</v>
-      </c>
-      <c r="AB16">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-      <c r="P17">
-        <v>17</v>
-      </c>
-      <c r="AB17">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="S18">
-        <v>12</v>
-      </c>
-      <c r="T18">
-        <v>24</v>
-      </c>
-      <c r="AB18">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="S19">
-        <v>12</v>
-      </c>
-      <c r="AB19">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>59</v>
-      </c>
-      <c r="R20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>60</v>
-      </c>
-      <c r="P21">
-        <v>35</v>
-      </c>
-      <c r="R21">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>61</v>
-      </c>
-      <c r="P22">
-        <v>35</v>
-      </c>
-      <c r="Q22">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
-      </c>
-      <c r="P23">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>63</v>
-      </c>
-      <c r="R24">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" t="s">
-        <v>65</v>
-      </c>
-      <c r="L25" t="s">
-        <v>66</v>
-      </c>
-      <c r="R25">
-        <v>35</v>
-      </c>
-      <c r="AA25">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" t="s">
-        <v>67</v>
-      </c>
-      <c r="P26">
-        <v>35</v>
-      </c>
-      <c r="AA26">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q27">
-        <v>35</v>
-      </c>
-      <c r="AA27">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" t="s">
-        <v>69</v>
-      </c>
-      <c r="P28">
-        <v>35</v>
-      </c>
-      <c r="AA28">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" t="s">
-        <v>70</v>
-      </c>
-      <c r="P29">
-        <v>17</v>
-      </c>
-      <c r="Q29">
-        <v>18</v>
-      </c>
-      <c r="R29">
-        <v>17</v>
-      </c>
-      <c r="AB29">
+      <c r="C38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB38">
         <v>30</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE680C0-63B3-41B9-B95E-254BF6DDF46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65161737-5290-4C4B-BE71-903203338F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="73">
   <si>
     <t>업무일자</t>
   </si>
@@ -113,57 +113,24 @@
     <t>프리백</t>
   </si>
   <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
     <t>김정신</t>
   </si>
   <si>
     <t>생산1부-미싱팀</t>
   </si>
   <si>
-    <t>2026-03-30 08:38:24.342420</t>
-  </si>
-  <si>
     <t>박은정</t>
   </si>
   <si>
-    <t>2026-03-30 08:33:11.796079</t>
-  </si>
-  <si>
     <t>최미숙</t>
   </si>
   <si>
-    <t>2026-03-30 06:32:42.754321</t>
-  </si>
-  <si>
     <t>홍숙란</t>
   </si>
   <si>
-    <t>2026-03-30 06:31:11.722982</t>
-  </si>
-  <si>
     <t>김은자</t>
   </si>
   <si>
-    <t>2026-03-30 03:57:12.838622</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-03-31 08:35:59.708201</t>
-  </si>
-  <si>
-    <t>2026-03-31 08:34:11.002186</t>
-  </si>
-  <si>
-    <t>2026-03-31 08:32:26.025604</t>
-  </si>
-  <si>
-    <t>2026-03-31 04:08:20.969021</t>
-  </si>
-  <si>
     <t>2026-04-01</t>
   </si>
   <si>
@@ -180,9 +147,6 @@
   </si>
   <si>
     <t>2026-04-01 04:09:30.387897</t>
-  </si>
-  <si>
-    <t>헤드하는~중</t>
   </si>
   <si>
     <t>2026-04-02</t>
@@ -634,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -723,13 +687,13 @@
         <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="V1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="W1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s">
         <v>20</v>
@@ -752,19 +716,19 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R2">
         <v>35</v>
@@ -775,16 +739,16 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="AC3">
         <v>25</v>
@@ -792,16 +756,16 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="Y4">
         <v>30</v>
@@ -809,16 +773,16 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="R5">
         <v>35</v>
@@ -829,19 +793,16 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="M6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z6">
-        <v>30</v>
+      <c r="Q6">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
@@ -849,19 +810,19 @@
         <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
       <c r="X7">
-        <v>4</v>
-      </c>
-      <c r="AB7">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="AC7">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
@@ -869,13 +830,16 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
+      </c>
+      <c r="Q8">
+        <v>17</v>
       </c>
       <c r="AC8">
         <v>25</v>
@@ -886,129 +850,132 @@
         <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
       </c>
+      <c r="T9">
+        <v>12</v>
+      </c>
+      <c r="U9">
+        <v>24</v>
+      </c>
       <c r="AC9">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z10">
-        <v>30</v>
-      </c>
-      <c r="AB10">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="T10">
+        <v>12</v>
+      </c>
+      <c r="AC10">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z11">
-        <v>30</v>
-      </c>
-      <c r="AA11">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="S11">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q12">
-        <v>18</v>
-      </c>
-      <c r="AB12">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="S12">
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB13">
-        <v>60</v>
+        <v>47</v>
+      </c>
+      <c r="Q13">
+        <v>35</v>
+      </c>
+      <c r="R13">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y14">
-        <v>30</v>
-      </c>
-      <c r="AB14">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="Q14">
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q15">
+        <v>49</v>
+      </c>
+      <c r="S15">
         <v>35</v>
       </c>
     </row>
@@ -1017,19 +984,22 @@
         <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" t="s">
         <v>52</v>
       </c>
-      <c r="X16">
-        <v>11</v>
-      </c>
-      <c r="AC16">
-        <v>25</v>
+      <c r="S16">
+        <v>35</v>
+      </c>
+      <c r="AB16">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
@@ -1037,19 +1007,19 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>53</v>
       </c>
       <c r="Q17">
-        <v>17</v>
-      </c>
-      <c r="AC17">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="AB17">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
@@ -1057,22 +1027,19 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
       </c>
-      <c r="T18">
-        <v>12</v>
-      </c>
-      <c r="U18">
-        <v>24</v>
-      </c>
-      <c r="AC18">
-        <v>25</v>
+      <c r="R18">
+        <v>35</v>
+      </c>
+      <c r="AB18">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
@@ -1080,150 +1047,153 @@
         <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
       </c>
-      <c r="T19">
-        <v>12</v>
-      </c>
-      <c r="AC19">
-        <v>25</v>
+      <c r="Q19">
+        <v>35</v>
+      </c>
+      <c r="AB19">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
         <v>56</v>
       </c>
-      <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
+      <c r="Q20">
+        <v>17</v>
+      </c>
+      <c r="R20">
+        <v>18</v>
       </c>
       <c r="S20">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="AC20">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q21">
-        <v>35</v>
-      </c>
-      <c r="S21">
-        <v>35</v>
+        <v>61</v>
+      </c>
+      <c r="L21" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC21">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q22">
-        <v>35</v>
-      </c>
-      <c r="R22">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="AB22">
+        <v>21</v>
+      </c>
+      <c r="AC22">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q23">
-        <v>35</v>
+        <v>64</v>
+      </c>
+      <c r="P23">
+        <v>35</v>
+      </c>
+      <c r="AC23">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
-      </c>
-      <c r="S24">
-        <v>35</v>
+        <v>65</v>
+      </c>
+      <c r="AC24">
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
-      </c>
-      <c r="M25" t="s">
-        <v>64</v>
-      </c>
-      <c r="S25">
-        <v>35</v>
-      </c>
-      <c r="AB25">
-        <v>30</v>
+        <v>67</v>
+      </c>
+      <c r="AA25">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q26">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AB26">
         <v>30</v>
@@ -1231,39 +1201,36 @@
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
-      </c>
-      <c r="R27">
-        <v>35</v>
-      </c>
-      <c r="AB27">
-        <v>30</v>
+        <v>69</v>
+      </c>
+      <c r="L27" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA27">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q28">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AB28">
         <v>30</v>
@@ -1271,192 +1238,18 @@
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q29">
-        <v>17</v>
-      </c>
-      <c r="R29">
-        <v>18</v>
-      </c>
-      <c r="S29">
-        <v>17</v>
-      </c>
-      <c r="AC29">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" t="s">
-        <v>73</v>
-      </c>
-      <c r="L30" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC30">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB31">
-        <v>21</v>
-      </c>
-      <c r="AC31">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" t="s">
-        <v>76</v>
-      </c>
-      <c r="P32">
-        <v>35</v>
-      </c>
-      <c r="AC32">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC33">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA34">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB35">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" t="s">
-        <v>81</v>
-      </c>
-      <c r="L36" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA36">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB37">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB38">
+      <c r="AB29">
         <v>30</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65161737-5290-4C4B-BE71-903203338F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE32C8D0-25C7-4BDD-8F70-FDEDC1B8CDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="78">
   <si>
     <t>업무일자</t>
   </si>
@@ -252,6 +252,21 @@
   </si>
   <si>
     <t>2026-04-07 04:10:50.737382</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-09 08:33:21.777049</t>
+  </si>
+  <si>
+    <t>2026-04-09 08:31:09.763602</t>
+  </si>
+  <si>
+    <t>2026-04-09 06:38:49.904129</t>
+  </si>
+  <si>
+    <t>2026-04-09 06:31:59.233825</t>
   </si>
 </sst>
 </file>
@@ -294,7 +309,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -1253,6 +1269,172 @@
         <v>30</v>
       </c>
     </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1">
+        <v>46</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE32C8D0-25C7-4BDD-8F70-FDEDC1B8CDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF02515-6B9A-473F-BFEF-B9AE3F614689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35770" yWindow="4400" windowWidth="12440" windowHeight="12260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="83">
   <si>
     <t>업무일자</t>
   </si>
@@ -267,6 +267,21 @@
   </si>
   <si>
     <t>2026-04-09 06:31:59.233825</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-10 08:34:24.305772</t>
+  </si>
+  <si>
+    <t>2026-04-10 08:31:05.736780</t>
+  </si>
+  <si>
+    <t>2026-04-10 06:33:11.448780</t>
+  </si>
+  <si>
+    <t>2026-04-10 06:32:19.460265</t>
   </si>
 </sst>
 </file>
@@ -309,8 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -614,32 +628,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.4140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -732,30 +722,24 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2">
-        <v>35</v>
-      </c>
-      <c r="AC2">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="X2">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
@@ -764,78 +748,81 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC3">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="P3">
+        <v>18</v>
+      </c>
+      <c r="Q3">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y4">
-        <v>30</v>
+        <v>81</v>
+      </c>
+      <c r="Q4">
+        <v>17</v>
+      </c>
+      <c r="AC4">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5">
+        <v>82</v>
+      </c>
+      <c r="P5">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q6">
-        <v>35</v>
+        <v>74</v>
+      </c>
+      <c r="AC6">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X7">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="AC7">
         <v>25</v>
@@ -843,42 +830,36 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8">
-        <v>17</v>
-      </c>
-      <c r="AC8">
-        <v>25</v>
+        <v>76</v>
+      </c>
+      <c r="P8">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="T9">
-        <v>12</v>
-      </c>
-      <c r="U9">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="AB9">
+        <v>46</v>
       </c>
       <c r="AC9">
         <v>25</v>
@@ -886,19 +867,19 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="T10">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>62</v>
       </c>
       <c r="AC10">
         <v>25</v>
@@ -906,7 +887,7 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -915,35 +896,38 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="S11">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="AB11">
+        <v>21</v>
+      </c>
+      <c r="AC11">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q12">
-        <v>35</v>
-      </c>
-      <c r="S12">
-        <v>35</v>
+        <v>64</v>
+      </c>
+      <c r="P12">
+        <v>35</v>
+      </c>
+      <c r="AC12">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -952,35 +936,32 @@
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q13">
-        <v>35</v>
-      </c>
-      <c r="R13">
-        <v>35</v>
+        <v>65</v>
+      </c>
+      <c r="AC13">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q14">
-        <v>35</v>
+        <v>67</v>
+      </c>
+      <c r="AA14">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
@@ -989,15 +970,15 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="S15">
-        <v>35</v>
+        <v>68</v>
+      </c>
+      <c r="AB15">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -1006,33 +987,27 @@
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" t="s">
-        <v>52</v>
-      </c>
-      <c r="S16">
-        <v>35</v>
-      </c>
-      <c r="AB16">
-        <v>30</v>
+        <v>69</v>
+      </c>
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA16">
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q17">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AB17">
         <v>30</v>
@@ -1040,7 +1015,7 @@
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -1049,10 +1024,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
-      </c>
-      <c r="R18">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AB18">
         <v>30</v>
@@ -1063,15 +1035,18 @@
         <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q19">
+        <v>51</v>
+      </c>
+      <c r="L19" t="s">
+        <v>52</v>
+      </c>
+      <c r="R19">
         <v>35</v>
       </c>
       <c r="AB19">
@@ -1083,70 +1058,64 @@
         <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q20">
-        <v>17</v>
-      </c>
-      <c r="R20">
-        <v>18</v>
-      </c>
-      <c r="S20">
-        <v>17</v>
-      </c>
-      <c r="AC20">
+        <v>53</v>
+      </c>
+      <c r="P20">
+        <v>35</v>
+      </c>
+      <c r="AB20">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC21">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="Q21">
+        <v>35</v>
+      </c>
+      <c r="AB21">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>55</v>
+      </c>
+      <c r="P22">
+        <v>35</v>
       </c>
       <c r="AB22">
-        <v>21</v>
-      </c>
-      <c r="AC22">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -1155,284 +1124,284 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="P23">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="Q23">
+        <v>18</v>
+      </c>
+      <c r="R23">
+        <v>17</v>
       </c>
       <c r="AC23">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC24">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="R24">
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA25">
-        <v>15</v>
+        <v>46</v>
+      </c>
+      <c r="P25">
+        <v>35</v>
+      </c>
+      <c r="R25">
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB26">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="P26">
+        <v>35</v>
+      </c>
+      <c r="Q26">
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
-      </c>
-      <c r="L27" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA27">
-        <v>11</v>
+        <v>48</v>
+      </c>
+      <c r="P27">
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB28">
-        <v>30</v>
+        <v>49</v>
+      </c>
+      <c r="R28">
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>39</v>
+      </c>
+      <c r="P29">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="X30">
+        <v>11</v>
+      </c>
+      <c r="AC30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>41</v>
+      </c>
+      <c r="P31">
+        <v>17</v>
+      </c>
+      <c r="AC31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="S32">
+        <v>12</v>
+      </c>
+      <c r="T32">
+        <v>24</v>
+      </c>
+      <c r="AC32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB29">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1">
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="S33">
+        <v>12</v>
+      </c>
+      <c r="AC33">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34">
+        <v>35</v>
+      </c>
+      <c r="AC34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1">
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC35">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="1" t="s">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y36">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1">
-        <v>18</v>
-      </c>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1">
-        <v>46</v>
-      </c>
-      <c r="AC33" s="1">
-        <v>25</v>
+      <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q37">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF02515-6B9A-473F-BFEF-B9AE3F614689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CB6F94-FE87-4228-9B26-C3008BF387C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35770" yWindow="4400" windowWidth="12440" windowHeight="12260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="96">
   <si>
     <t>업무일자</t>
   </si>
@@ -282,6 +282,45 @@
   </si>
   <si>
     <t>2026-04-10 06:32:19.460265</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-14 08:33:30.432843</t>
+  </si>
+  <si>
+    <t>2026-04-14 08:31:57.184459</t>
+  </si>
+  <si>
+    <t>2026-04-14 06:40:28.215216</t>
+  </si>
+  <si>
+    <t>2026-04-14 06:40:16.919264</t>
+  </si>
+  <si>
+    <t>2026-04-14 06:31:14.519573</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-13 08:33:55.063877</t>
+  </si>
+  <si>
+    <t>2026-04-13 06:37:16.635776</t>
+  </si>
+  <si>
+    <t>2026-04-13 06:35:47.780400</t>
+  </si>
+  <si>
+    <t>백커버.바닐라.하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-13 06:31:45.982494</t>
+  </si>
+  <si>
+    <t>2026-04-13 06:31:23.286535</t>
   </si>
 </sst>
 </file>
@@ -628,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
@@ -722,7 +761,7 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -731,15 +770,18 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="X2">
-        <v>15</v>
+        <v>84</v>
+      </c>
+      <c r="P2">
+        <v>35</v>
+      </c>
+      <c r="Q2">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
@@ -748,18 +790,18 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P3">
-        <v>18</v>
-      </c>
-      <c r="Q3">
-        <v>52</v>
+        <v>85</v>
+      </c>
+      <c r="AB3">
+        <v>30</v>
+      </c>
+      <c r="AC3">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -768,10 +810,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q4">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="AC4">
         <v>25</v>
@@ -779,58 +818,64 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="P5">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="AC5">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC6">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="AB6">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC7">
-        <v>25</v>
+        <v>90</v>
+      </c>
+      <c r="P7">
+        <v>18</v>
+      </c>
+      <c r="Q7">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -839,183 +884,186 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="P8">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB9">
-        <v>46</v>
-      </c>
-      <c r="AC9">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="L9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P9">
+        <v>17</v>
+      </c>
+      <c r="Q9">
+        <v>37</v>
+      </c>
+      <c r="R9">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC10">
-        <v>25</v>
+        <v>94</v>
+      </c>
+      <c r="P10">
+        <v>18</v>
+      </c>
+      <c r="Q10">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB11">
-        <v>21</v>
-      </c>
-      <c r="AC11">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="Q11">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="P12">
-        <v>35</v>
-      </c>
-      <c r="AC12">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="X12">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC13">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="P13">
+        <v>18</v>
+      </c>
+      <c r="Q13">
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA14">
-        <v>15</v>
+        <v>81</v>
+      </c>
+      <c r="Q14">
+        <v>17</v>
+      </c>
+      <c r="AC14">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB15">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P15">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="L16" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA16">
-        <v>11</v>
+        <v>74</v>
+      </c>
+      <c r="AC16">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB17">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="AC17">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -1024,124 +1072,112 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB18">
-        <v>30</v>
+        <v>76</v>
+      </c>
+      <c r="P18">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" t="s">
-        <v>52</v>
-      </c>
-      <c r="R19">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="AB19">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="AC19">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
-      </c>
-      <c r="P20">
-        <v>35</v>
-      </c>
-      <c r="AB20">
-        <v>30</v>
+        <v>61</v>
+      </c>
+      <c r="L20" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC20">
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q21">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AB21">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="AC21">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P22">
         <v>35</v>
       </c>
-      <c r="AB22">
-        <v>30</v>
+      <c r="AC22">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
-      </c>
-      <c r="P23">
-        <v>17</v>
-      </c>
-      <c r="Q23">
-        <v>18</v>
-      </c>
-      <c r="R23">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="AC23">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
@@ -1150,55 +1186,52 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
-      </c>
-      <c r="R24">
-        <v>35</v>
+        <v>67</v>
+      </c>
+      <c r="AA24">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P25">
-        <v>35</v>
-      </c>
-      <c r="R25">
-        <v>35</v>
+        <v>68</v>
+      </c>
+      <c r="AB25">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
-      </c>
-      <c r="P26">
-        <v>35</v>
-      </c>
-      <c r="Q26">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="L26" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA26">
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
@@ -1207,32 +1240,32 @@
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
-      </c>
-      <c r="P27">
-        <v>35</v>
+        <v>71</v>
+      </c>
+      <c r="AB27">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
-      </c>
-      <c r="R28">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="AB28">
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
@@ -1241,15 +1274,21 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
-      </c>
-      <c r="P29">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="L29" t="s">
+        <v>52</v>
+      </c>
+      <c r="R29">
+        <v>35</v>
+      </c>
+      <c r="AB29">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
@@ -1258,149 +1297,343 @@
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
-      </c>
-      <c r="X30">
-        <v>11</v>
-      </c>
-      <c r="AC30">
-        <v>25</v>
+        <v>53</v>
+      </c>
+      <c r="P30">
+        <v>35</v>
+      </c>
+      <c r="AB30">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
-      </c>
-      <c r="P31">
-        <v>17</v>
-      </c>
-      <c r="AC31">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="Q31">
+        <v>35</v>
+      </c>
+      <c r="AB31">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
-      </c>
-      <c r="S32">
-        <v>12</v>
-      </c>
-      <c r="T32">
-        <v>24</v>
-      </c>
-      <c r="AC32">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="P32">
+        <v>35</v>
+      </c>
+      <c r="AB32">
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
-      </c>
-      <c r="S33">
-        <v>12</v>
+        <v>56</v>
+      </c>
+      <c r="P33">
+        <v>17</v>
+      </c>
+      <c r="Q33">
+        <v>18</v>
+      </c>
+      <c r="R33">
+        <v>17</v>
       </c>
       <c r="AC33">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L34" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q34">
-        <v>35</v>
-      </c>
-      <c r="AC34">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="R34">
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC35">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="P35">
+        <v>35</v>
+      </c>
+      <c r="R35">
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y36">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="P36">
+        <v>35</v>
+      </c>
+      <c r="Q36">
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="P37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>49</v>
+      </c>
+      <c r="R38">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
+        <v>39</v>
+      </c>
+      <c r="P39">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="X40">
+        <v>11</v>
+      </c>
+      <c r="AC40">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
+        <v>41</v>
+      </c>
+      <c r="P41">
+        <v>17</v>
+      </c>
+      <c r="AC41">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
+        <v>42</v>
+      </c>
+      <c r="S42">
+        <v>12</v>
+      </c>
+      <c r="T42">
+        <v>24</v>
+      </c>
+      <c r="AC42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s">
+        <v>43</v>
+      </c>
+      <c r="S43">
+        <v>12</v>
+      </c>
+      <c r="AC43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
         <v>32</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q44">
+        <v>35</v>
+      </c>
+      <c r="AC44">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" t="s">
         <v>31</v>
       </c>
-      <c r="C37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
         <v>37</v>
       </c>
-      <c r="Q37">
+      <c r="Q47">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CB6F94-FE87-4228-9B26-C3008BF387C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F002C8E-1446-4D06-8EDB-F60F8508D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="112">
   <si>
     <t>업무일자</t>
   </si>
@@ -321,6 +321,54 @@
   </si>
   <si>
     <t>2026-04-13 06:31:23.286535</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-17 06:36:19.249837</t>
+  </si>
+  <si>
+    <t>헤드.바닐라.하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-17 06:33:54.428918</t>
+  </si>
+  <si>
+    <t>2026-04-17 06:31:11.488740</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-16 08:56:25.207707</t>
+  </si>
+  <si>
+    <t>2026-04-16 08:33:46.005818</t>
+  </si>
+  <si>
+    <t>2026-04-16 06:35:00.664368</t>
+  </si>
+  <si>
+    <t>2026-04-16 06:34:14.421242</t>
+  </si>
+  <si>
+    <t>2026-04-16 06:33:53.637244</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-15 23:27:03.607224</t>
+  </si>
+  <si>
+    <t>백커버.(세이)마무리~중</t>
+  </si>
+  <si>
+    <t>2026-04-15 09:32:32.595943</t>
+  </si>
+  <si>
+    <t>2026-04-15 08:33:27.066216</t>
   </si>
 </sst>
 </file>
@@ -667,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
@@ -761,27 +809,30 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>97</v>
+      </c>
+      <c r="L2" t="s">
+        <v>98</v>
       </c>
       <c r="P2">
         <v>35</v>
       </c>
-      <c r="Q2">
-        <v>18</v>
+      <c r="AA2">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
@@ -790,27 +841,24 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB3">
-        <v>30</v>
-      </c>
-      <c r="AC3">
-        <v>25</v>
+        <v>99</v>
+      </c>
+      <c r="Q3">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="AC4">
         <v>25</v>
@@ -818,19 +866,19 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P5">
-        <v>18</v>
+        <v>102</v>
+      </c>
+      <c r="AB5">
+        <v>59</v>
       </c>
       <c r="AC5">
         <v>25</v>
@@ -838,107 +886,98 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB6">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="AC6">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="P7">
-        <v>18</v>
-      </c>
-      <c r="Q7">
-        <v>17</v>
+        <v>104</v>
+      </c>
+      <c r="AB7">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="P8">
-        <v>35</v>
+        <v>105</v>
+      </c>
+      <c r="AC8">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" t="s">
-        <v>93</v>
-      </c>
-      <c r="P9">
-        <v>17</v>
-      </c>
-      <c r="Q9">
-        <v>37</v>
-      </c>
-      <c r="R9">
-        <v>18</v>
+        <v>106</v>
+      </c>
+      <c r="AB9">
+        <v>30</v>
+      </c>
+      <c r="AC9">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P10">
-        <v>18</v>
-      </c>
-      <c r="Q10">
-        <v>17</v>
+        <v>108</v>
+      </c>
+      <c r="L10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB10">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -947,15 +986,15 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q11">
-        <v>35</v>
+        <v>110</v>
+      </c>
+      <c r="AC11">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
@@ -964,47 +1003,47 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
-      </c>
-      <c r="X12">
-        <v>15</v>
+        <v>111</v>
+      </c>
+      <c r="AC12">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P13">
+        <v>35</v>
+      </c>
+      <c r="Q13">
         <v>18</v>
-      </c>
-      <c r="Q13">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q14">
-        <v>17</v>
+        <v>85</v>
+      </c>
+      <c r="AB14">
+        <v>30</v>
       </c>
       <c r="AC14">
         <v>25</v>
@@ -1012,33 +1051,36 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="P15">
-        <v>35</v>
+        <v>86</v>
+      </c>
+      <c r="AC15">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>87</v>
+      </c>
+      <c r="P16">
+        <v>18</v>
       </c>
       <c r="AC16">
         <v>25</v>
@@ -1046,61 +1088,61 @@
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC17">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="AB17">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="P18">
         <v>18</v>
       </c>
+      <c r="Q18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB19">
-        <v>46</v>
-      </c>
-      <c r="AC19">
-        <v>25</v>
+        <v>91</v>
+      </c>
+      <c r="P19">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -1109,38 +1151,44 @@
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="L20" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC20">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="P20">
+        <v>17</v>
+      </c>
+      <c r="Q20">
+        <v>37</v>
+      </c>
+      <c r="R20">
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB21">
-        <v>21</v>
-      </c>
-      <c r="AC21">
-        <v>25</v>
+        <v>94</v>
+      </c>
+      <c r="P21">
+        <v>18</v>
+      </c>
+      <c r="Q21">
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
@@ -1149,206 +1197,200 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="P22">
-        <v>35</v>
-      </c>
-      <c r="AC22">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="Q22">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC23">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="X23">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA24">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="P24">
+        <v>18</v>
+      </c>
+      <c r="Q24">
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB25">
-        <v>30</v>
+        <v>81</v>
+      </c>
+      <c r="Q25">
+        <v>17</v>
+      </c>
+      <c r="AC25">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
-      </c>
-      <c r="L26" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA26">
-        <v>11</v>
+        <v>82</v>
+      </c>
+      <c r="P26">
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB27">
-        <v>30</v>
+        <v>74</v>
+      </c>
+      <c r="AC27">
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB28">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="AC28">
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
-      </c>
-      <c r="L29" t="s">
-        <v>52</v>
-      </c>
-      <c r="R29">
-        <v>35</v>
-      </c>
-      <c r="AB29">
-        <v>30</v>
+        <v>76</v>
+      </c>
+      <c r="P29">
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
-      </c>
-      <c r="P30">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="AB30">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="AC30">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q31">
-        <v>35</v>
-      </c>
-      <c r="AB31">
-        <v>30</v>
+        <v>61</v>
+      </c>
+      <c r="L31" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC31">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
-      </c>
-      <c r="P32">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AB32">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="AC32">
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
         <v>29</v>
@@ -1357,272 +1399,269 @@
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="P33">
-        <v>17</v>
-      </c>
-      <c r="Q33">
-        <v>18</v>
-      </c>
-      <c r="R33">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="AC33">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
-      </c>
-      <c r="R34">
-        <v>35</v>
+        <v>65</v>
+      </c>
+      <c r="AC34">
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
-      </c>
-      <c r="P35">
-        <v>35</v>
-      </c>
-      <c r="R35">
-        <v>35</v>
+        <v>67</v>
+      </c>
+      <c r="AA35">
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
-      </c>
-      <c r="P36">
-        <v>35</v>
-      </c>
-      <c r="Q36">
-        <v>35</v>
+        <v>68</v>
+      </c>
+      <c r="AB36">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
-      </c>
-      <c r="P37">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="L37" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA37">
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>49</v>
-      </c>
-      <c r="R38">
-        <v>35</v>
+        <v>71</v>
+      </c>
+      <c r="AB38">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
-      </c>
-      <c r="P39">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="AB39">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
-      </c>
-      <c r="X40">
-        <v>11</v>
-      </c>
-      <c r="AC40">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="L40" t="s">
+        <v>52</v>
+      </c>
+      <c r="R40">
+        <v>35</v>
+      </c>
+      <c r="AB40">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P41">
-        <v>17</v>
-      </c>
-      <c r="AC41">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="AB41">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
-      </c>
-      <c r="S42">
-        <v>12</v>
-      </c>
-      <c r="T42">
-        <v>24</v>
-      </c>
-      <c r="AC42">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="Q42">
+        <v>35</v>
+      </c>
+      <c r="AB42">
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
-      </c>
-      <c r="S43">
-        <v>12</v>
-      </c>
-      <c r="AC43">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="P43">
+        <v>35</v>
+      </c>
+      <c r="AB43">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
-      </c>
-      <c r="L44" t="s">
-        <v>34</v>
+        <v>56</v>
+      </c>
+      <c r="P44">
+        <v>17</v>
       </c>
       <c r="Q44">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="R44">
+        <v>17</v>
       </c>
       <c r="AC44">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC45">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="R45">
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y46">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="P46">
+        <v>35</v>
+      </c>
+      <c r="R46">
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
         <v>31</v>
@@ -1631,9 +1670,220 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
+        <v>47</v>
+      </c>
+      <c r="P47">
+        <v>35</v>
+      </c>
+      <c r="Q47">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
+        <v>48</v>
+      </c>
+      <c r="P48">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>49</v>
+      </c>
+      <c r="R49">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>39</v>
+      </c>
+      <c r="P50">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="X51">
+        <v>11</v>
+      </c>
+      <c r="AC51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s">
+        <v>41</v>
+      </c>
+      <c r="P52">
+        <v>17</v>
+      </c>
+      <c r="AC52">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s">
+        <v>42</v>
+      </c>
+      <c r="S53">
+        <v>12</v>
+      </c>
+      <c r="T53">
+        <v>24</v>
+      </c>
+      <c r="AC53">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" t="s">
+        <v>43</v>
+      </c>
+      <c r="S54">
+        <v>12</v>
+      </c>
+      <c r="AC54">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>32</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" t="s">
+        <v>33</v>
+      </c>
+      <c r="L55" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q55">
+        <v>35</v>
+      </c>
+      <c r="AC55">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC56">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y57">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s">
         <v>37</v>
       </c>
-      <c r="Q47">
+      <c r="Q58">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F002C8E-1446-4D06-8EDB-F60F8508D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F22531F-0306-4CD6-B179-83F6FDAB8606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="125">
   <si>
     <t>업무일자</t>
   </si>
@@ -369,6 +369,45 @@
   </si>
   <si>
     <t>2026-04-15 08:33:27.066216</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-21 08:54:45.577182</t>
+  </si>
+  <si>
+    <t>2026-04-21 08:34:20.575954</t>
+  </si>
+  <si>
+    <t>2026-04-21 06:38:07.555705</t>
+  </si>
+  <si>
+    <t>2026-04-21 06:36:20.174528</t>
+  </si>
+  <si>
+    <t>2026-04-21 06:33:50.113214</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-20 08:33:59.068070</t>
+  </si>
+  <si>
+    <t>2026-04-20 08:30:42.988539</t>
+  </si>
+  <si>
+    <t>2026-04-20 06:35:24.098749</t>
+  </si>
+  <si>
+    <t>2026-04-20 06:33:25.687819</t>
+  </si>
+  <si>
+    <t>2026-04-20 03:48:15.055903</t>
+  </si>
+  <si>
+    <t>전용1열.올리브.하는~중</t>
   </si>
 </sst>
 </file>
@@ -715,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
@@ -809,241 +848,244 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P2">
-        <v>35</v>
-      </c>
-      <c r="AA2">
-        <v>15</v>
+        <v>113</v>
+      </c>
+      <c r="Q2">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q3">
-        <v>35</v>
+        <v>114</v>
+      </c>
+      <c r="P3">
+        <v>35</v>
+      </c>
+      <c r="AC3">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC4">
-        <v>25</v>
+        <v>115</v>
+      </c>
+      <c r="L4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z4">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="AB5">
-        <v>59</v>
-      </c>
-      <c r="AC5">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC6">
-        <v>25</v>
+        <v>117</v>
+      </c>
+      <c r="Q6">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB7">
-        <v>30</v>
+        <v>119</v>
+      </c>
+      <c r="Q7">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC8">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P8">
+        <v>35</v>
+      </c>
+      <c r="S8">
+        <v>12</v>
+      </c>
+      <c r="Y8">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB9">
-        <v>30</v>
-      </c>
-      <c r="AC9">
-        <v>25</v>
+        <v>121</v>
+      </c>
+      <c r="P9">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="L10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB10">
-        <v>30</v>
+        <v>122</v>
+      </c>
+      <c r="P10">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC11">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="L11" t="s">
+        <v>124</v>
+      </c>
+      <c r="P11">
+        <v>18</v>
+      </c>
+      <c r="Q11">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC12">
-        <v>25</v>
+        <v>97</v>
+      </c>
+      <c r="L12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P12">
+        <v>35</v>
+      </c>
+      <c r="AA12">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="P13">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="Q13">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB14">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AC14">
         <v>25</v>
@@ -1051,7 +1093,7 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -1060,7 +1102,10 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>102</v>
+      </c>
+      <c r="AB15">
+        <v>59</v>
       </c>
       <c r="AC15">
         <v>25</v>
@@ -1068,19 +1113,16 @@
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="P16">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="AC16">
         <v>25</v>
@@ -1088,7 +1130,7 @@
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -1097,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="AB17">
         <v>30</v>
@@ -1105,44 +1147,44 @@
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
-      </c>
-      <c r="P18">
-        <v>18</v>
-      </c>
-      <c r="Q18">
-        <v>17</v>
+        <v>105</v>
+      </c>
+      <c r="AC18">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
-      </c>
-      <c r="P19">
-        <v>35</v>
+        <v>106</v>
+      </c>
+      <c r="AB19">
+        <v>30</v>
+      </c>
+      <c r="AC19">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -1151,61 +1193,52 @@
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s">
-        <v>93</v>
-      </c>
-      <c r="P20">
-        <v>17</v>
-      </c>
-      <c r="Q20">
-        <v>37</v>
-      </c>
-      <c r="R20">
-        <v>18</v>
+        <v>109</v>
+      </c>
+      <c r="AB20">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
-      </c>
-      <c r="P21">
-        <v>18</v>
-      </c>
-      <c r="Q21">
-        <v>17</v>
+        <v>110</v>
+      </c>
+      <c r="AC21">
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q22">
-        <v>35</v>
+        <v>111</v>
+      </c>
+      <c r="AC22">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -1214,15 +1247,18 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="X23">
-        <v>15</v>
+        <v>84</v>
+      </c>
+      <c r="P23">
+        <v>35</v>
+      </c>
+      <c r="Q23">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
@@ -1231,18 +1267,18 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
-      </c>
-      <c r="P24">
-        <v>18</v>
-      </c>
-      <c r="Q24">
-        <v>52</v>
+        <v>85</v>
+      </c>
+      <c r="AB24">
+        <v>30</v>
+      </c>
+      <c r="AC24">
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1251,10 +1287,7 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q25">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="AC25">
         <v>25</v>
@@ -1262,58 +1295,64 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="P26">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="AC26">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC27">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="AB27">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC28">
-        <v>25</v>
+        <v>90</v>
+      </c>
+      <c r="P28">
+        <v>18</v>
+      </c>
+      <c r="Q28">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -1322,183 +1361,186 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="P29">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB30">
-        <v>46</v>
-      </c>
-      <c r="AC30">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="L30" t="s">
+        <v>93</v>
+      </c>
+      <c r="P30">
+        <v>17</v>
+      </c>
+      <c r="Q30">
+        <v>37</v>
+      </c>
+      <c r="R30">
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC31">
-        <v>25</v>
+        <v>94</v>
+      </c>
+      <c r="P31">
+        <v>18</v>
+      </c>
+      <c r="Q31">
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB32">
-        <v>21</v>
-      </c>
-      <c r="AC32">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="Q32">
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P33">
-        <v>35</v>
-      </c>
-      <c r="AC33">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="X33">
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC34">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="P34">
+        <v>18</v>
+      </c>
+      <c r="Q34">
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA35">
-        <v>15</v>
+        <v>81</v>
+      </c>
+      <c r="Q35">
+        <v>17</v>
+      </c>
+      <c r="AC35">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB36">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P36">
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
-      </c>
-      <c r="L37" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA37">
-        <v>11</v>
+        <v>74</v>
+      </c>
+      <c r="AC37">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB38">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="AC38">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
@@ -1507,124 +1549,112 @@
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB39">
-        <v>30</v>
+        <v>76</v>
+      </c>
+      <c r="P39">
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
-      </c>
-      <c r="L40" t="s">
-        <v>52</v>
-      </c>
-      <c r="R40">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="AB40">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="AC40">
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
-      </c>
-      <c r="P41">
-        <v>35</v>
-      </c>
-      <c r="AB41">
-        <v>30</v>
+        <v>61</v>
+      </c>
+      <c r="L41" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC41">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q42">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AB42">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="AC42">
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P43">
         <v>35</v>
       </c>
-      <c r="AB43">
-        <v>30</v>
+      <c r="AC43">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
-      </c>
-      <c r="P44">
-        <v>17</v>
-      </c>
-      <c r="Q44">
-        <v>18</v>
-      </c>
-      <c r="R44">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="AC44">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
         <v>28</v>
@@ -1633,55 +1663,52 @@
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
-      </c>
-      <c r="R45">
-        <v>35</v>
+        <v>67</v>
+      </c>
+      <c r="AA45">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
-      </c>
-      <c r="P46">
-        <v>35</v>
-      </c>
-      <c r="R46">
-        <v>35</v>
+        <v>68</v>
+      </c>
+      <c r="AB46">
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
-      </c>
-      <c r="P47">
-        <v>35</v>
-      </c>
-      <c r="Q47">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="L47" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA47">
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
         <v>30</v>
@@ -1690,32 +1717,32 @@
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
-      </c>
-      <c r="P48">
-        <v>35</v>
+        <v>71</v>
+      </c>
+      <c r="AB48">
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
-      </c>
-      <c r="R49">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="AB49">
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
@@ -1724,15 +1751,21 @@
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
-      </c>
-      <c r="P50">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="L50" t="s">
+        <v>52</v>
+      </c>
+      <c r="R50">
+        <v>35</v>
+      </c>
+      <c r="AB50">
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
         <v>28</v>
@@ -1741,149 +1774,343 @@
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
-      </c>
-      <c r="X51">
-        <v>11</v>
-      </c>
-      <c r="AC51">
-        <v>25</v>
+        <v>53</v>
+      </c>
+      <c r="P51">
+        <v>35</v>
+      </c>
+      <c r="AB51">
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
-      </c>
-      <c r="P52">
-        <v>17</v>
-      </c>
-      <c r="AC52">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="Q52">
+        <v>35</v>
+      </c>
+      <c r="AB52">
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
-      </c>
-      <c r="S53">
-        <v>12</v>
-      </c>
-      <c r="T53">
-        <v>24</v>
-      </c>
-      <c r="AC53">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="P53">
+        <v>35</v>
+      </c>
+      <c r="AB53">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
-      </c>
-      <c r="S54">
-        <v>12</v>
+        <v>56</v>
+      </c>
+      <c r="P54">
+        <v>17</v>
+      </c>
+      <c r="Q54">
+        <v>18</v>
+      </c>
+      <c r="R54">
+        <v>17</v>
       </c>
       <c r="AC54">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>33</v>
-      </c>
-      <c r="L55" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q55">
-        <v>35</v>
-      </c>
-      <c r="AC55">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="R55">
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC56">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="P56">
+        <v>35</v>
+      </c>
+      <c r="R56">
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y57">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="P57">
+        <v>35</v>
+      </c>
+      <c r="Q57">
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s">
+        <v>48</v>
+      </c>
+      <c r="P58">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" t="s">
+        <v>49</v>
+      </c>
+      <c r="R59">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" t="s">
+        <v>39</v>
+      </c>
+      <c r="P60">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" t="s">
+        <v>40</v>
+      </c>
+      <c r="X61">
+        <v>11</v>
+      </c>
+      <c r="AC61">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s">
+        <v>41</v>
+      </c>
+      <c r="P62">
+        <v>17</v>
+      </c>
+      <c r="AC62">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+      <c r="S63">
+        <v>12</v>
+      </c>
+      <c r="T63">
+        <v>24</v>
+      </c>
+      <c r="AC63">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s">
+        <v>43</v>
+      </c>
+      <c r="S64">
+        <v>12</v>
+      </c>
+      <c r="AC64">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
         <v>32</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" t="s">
+        <v>33</v>
+      </c>
+      <c r="L65" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q65">
+        <v>35</v>
+      </c>
+      <c r="AC65">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>32</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC66">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y67">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>32</v>
+      </c>
+      <c r="B68" t="s">
         <v>31</v>
       </c>
-      <c r="C58" t="s">
-        <v>27</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s">
         <v>37</v>
       </c>
-      <c r="Q58">
+      <c r="Q68">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F22531F-0306-4CD6-B179-83F6FDAB8606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91EACD8-65DF-45B3-BB3A-4CE350291369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="133">
   <si>
     <t>업무일자</t>
   </si>
@@ -408,6 +408,30 @@
   </si>
   <si>
     <t>전용1열.올리브.하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-23 06:34:13.779172</t>
+  </si>
+  <si>
+    <t>2026-04-23 06:32:51.319250</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-22 08:34:11.614846</t>
+  </si>
+  <si>
+    <t>2026-04-22 06:34:57.453317</t>
+  </si>
+  <si>
+    <t>2026-04-22 06:34:44.868066</t>
+  </si>
+  <si>
+    <t>2026-04-22 06:34:35.807283</t>
   </si>
 </sst>
 </file>
@@ -754,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
@@ -848,81 +872,87 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q2">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="P2">
+        <v>35</v>
+      </c>
+      <c r="AB2">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="P3">
-        <v>35</v>
-      </c>
-      <c r="AC3">
-        <v>25</v>
+        <v>127</v>
+      </c>
+      <c r="Q3">
+        <v>18</v>
+      </c>
+      <c r="AB3">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="L4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z4">
-        <v>30</v>
+        <v>129</v>
+      </c>
+      <c r="T4">
+        <v>24</v>
+      </c>
+      <c r="AC4">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB5">
-        <v>60</v>
+        <v>130</v>
+      </c>
+      <c r="Q5">
+        <v>35</v>
+      </c>
+      <c r="AC5">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -931,7 +961,10 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>131</v>
+      </c>
+      <c r="P6">
+        <v>18</v>
       </c>
       <c r="Q6">
         <v>35</v>
@@ -939,136 +972,124 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q7">
+        <v>132</v>
+      </c>
+      <c r="P7">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="P8">
-        <v>35</v>
-      </c>
-      <c r="S8">
-        <v>12</v>
-      </c>
-      <c r="Y8">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="Q8">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="P9">
         <v>35</v>
+      </c>
+      <c r="AC9">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="P10">
-        <v>35</v>
+        <v>115</v>
+      </c>
+      <c r="L10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z10">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="L11" t="s">
-        <v>124</v>
-      </c>
-      <c r="P11">
-        <v>18</v>
-      </c>
-      <c r="Q11">
-        <v>35</v>
+        <v>116</v>
+      </c>
+      <c r="AB11">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="L12" t="s">
-        <v>98</v>
-      </c>
-      <c r="P12">
-        <v>35</v>
-      </c>
-      <c r="AA12">
-        <v>15</v>
+        <v>117</v>
+      </c>
+      <c r="Q12">
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="Q13">
         <v>35</v>
@@ -1076,78 +1097,87 @@
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC14">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P14">
+        <v>35</v>
+      </c>
+      <c r="S14">
+        <v>12</v>
+      </c>
+      <c r="Y14">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB15">
-        <v>59</v>
-      </c>
-      <c r="AC15">
-        <v>25</v>
+        <v>121</v>
+      </c>
+      <c r="P15">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC16">
-        <v>25</v>
+        <v>122</v>
+      </c>
+      <c r="P16">
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB17">
-        <v>30</v>
+        <v>123</v>
+      </c>
+      <c r="L17" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17">
+        <v>18</v>
+      </c>
+      <c r="Q17">
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -1156,15 +1186,21 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC18">
-        <v>25</v>
+        <v>97</v>
+      </c>
+      <c r="L18" t="s">
+        <v>98</v>
+      </c>
+      <c r="P18">
+        <v>35</v>
+      </c>
+      <c r="AA18">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
@@ -1173,55 +1209,52 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB19">
-        <v>30</v>
-      </c>
-      <c r="AC19">
-        <v>25</v>
+        <v>99</v>
+      </c>
+      <c r="Q19">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="L20" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB20">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="AC20">
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="AB21">
+        <v>59</v>
       </c>
       <c r="AC21">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -1230,7 +1263,7 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="AC22">
         <v>25</v>
@@ -1238,39 +1271,33 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="P23">
-        <v>35</v>
-      </c>
-      <c r="Q23">
-        <v>18</v>
+        <v>104</v>
+      </c>
+      <c r="AB23">
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB24">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="AC24">
         <v>25</v>
@@ -1278,16 +1305,19 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>106</v>
+      </c>
+      <c r="AB25">
+        <v>30</v>
       </c>
       <c r="AC25">
         <v>25</v>
@@ -1295,7 +1325,7 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -1304,35 +1334,35 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
-      </c>
-      <c r="P26">
-        <v>18</v>
-      </c>
-      <c r="AC26">
-        <v>25</v>
+        <v>108</v>
+      </c>
+      <c r="L26" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB26">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB27">
-        <v>30</v>
+        <v>110</v>
+      </c>
+      <c r="AC27">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
@@ -1341,135 +1371,129 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
-      </c>
-      <c r="P28">
-        <v>18</v>
-      </c>
-      <c r="Q28">
-        <v>17</v>
+        <v>111</v>
+      </c>
+      <c r="AC28">
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="P29">
         <v>35</v>
+      </c>
+      <c r="Q29">
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
-      </c>
-      <c r="L30" t="s">
-        <v>93</v>
-      </c>
-      <c r="P30">
-        <v>17</v>
-      </c>
-      <c r="Q30">
-        <v>37</v>
-      </c>
-      <c r="R30">
-        <v>18</v>
+        <v>85</v>
+      </c>
+      <c r="AB30">
+        <v>30</v>
+      </c>
+      <c r="AC30">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
-      </c>
-      <c r="P31">
-        <v>18</v>
-      </c>
-      <c r="Q31">
-        <v>17</v>
+        <v>86</v>
+      </c>
+      <c r="AC31">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q32">
-        <v>35</v>
+        <v>87</v>
+      </c>
+      <c r="P32">
+        <v>18</v>
+      </c>
+      <c r="AC32">
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
-      </c>
-      <c r="X33">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="AB33">
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P34">
         <v>18</v>
       </c>
       <c r="Q34">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -1478,52 +1502,61 @@
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q35">
-        <v>17</v>
-      </c>
-      <c r="AC35">
-        <v>25</v>
+        <v>91</v>
+      </c>
+      <c r="P35">
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>92</v>
+      </c>
+      <c r="L36" t="s">
+        <v>93</v>
       </c>
       <c r="P36">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="Q36">
+        <v>37</v>
+      </c>
+      <c r="R36">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC37">
-        <v>25</v>
+        <v>94</v>
+      </c>
+      <c r="P37">
+        <v>18</v>
+      </c>
+      <c r="Q37">
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
         <v>29</v>
@@ -1532,64 +1565,64 @@
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC38">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="Q38">
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
-      </c>
-      <c r="P39">
-        <v>18</v>
+        <v>79</v>
+      </c>
+      <c r="X39">
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB40">
-        <v>46</v>
-      </c>
-      <c r="AC40">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="P40">
+        <v>18</v>
+      </c>
+      <c r="Q40">
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
-      </c>
-      <c r="L41" t="s">
-        <v>62</v>
+        <v>81</v>
+      </c>
+      <c r="Q41">
+        <v>17</v>
       </c>
       <c r="AC41">
         <v>25</v>
@@ -1597,39 +1630,33 @@
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB42">
-        <v>21</v>
-      </c>
-      <c r="AC42">
-        <v>25</v>
+        <v>82</v>
+      </c>
+      <c r="P42">
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
-      </c>
-      <c r="P43">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AC43">
         <v>25</v>
@@ -1637,16 +1664,16 @@
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AC44">
         <v>25</v>
@@ -1654,41 +1681,44 @@
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA45">
-        <v>15</v>
+        <v>76</v>
+      </c>
+      <c r="P45">
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="AB46">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="AC46">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
@@ -1697,75 +1727,75 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L47" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA47">
-        <v>11</v>
+        <v>62</v>
+      </c>
+      <c r="AC47">
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AB48">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="AC48">
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB49">
-        <v>30</v>
+        <v>64</v>
+      </c>
+      <c r="P49">
+        <v>35</v>
+      </c>
+      <c r="AC49">
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
-      </c>
-      <c r="L50" t="s">
-        <v>52</v>
-      </c>
-      <c r="R50">
-        <v>35</v>
-      </c>
-      <c r="AB50">
-        <v>30</v>
+        <v>65</v>
+      </c>
+      <c r="AC50">
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
         <v>28</v>
@@ -1774,30 +1804,24 @@
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
-      </c>
-      <c r="P51">
-        <v>35</v>
-      </c>
-      <c r="AB51">
-        <v>30</v>
+        <v>67</v>
+      </c>
+      <c r="AA51">
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q52">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AB52">
         <v>30</v>
@@ -1805,70 +1829,61 @@
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
-      </c>
-      <c r="P53">
-        <v>35</v>
-      </c>
-      <c r="AB53">
-        <v>30</v>
+        <v>69</v>
+      </c>
+      <c r="L53" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA53">
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
-      </c>
-      <c r="P54">
-        <v>17</v>
-      </c>
-      <c r="Q54">
-        <v>18</v>
-      </c>
-      <c r="R54">
-        <v>17</v>
-      </c>
-      <c r="AC54">
+        <v>71</v>
+      </c>
+      <c r="AB54">
         <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
-      </c>
-      <c r="R55">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="AB55">
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
         <v>26</v>
@@ -1877,89 +1892,107 @@
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
-      </c>
-      <c r="P56">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="L56" t="s">
+        <v>52</v>
       </c>
       <c r="R56">
         <v>35</v>
+      </c>
+      <c r="AB56">
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P57">
         <v>35</v>
       </c>
-      <c r="Q57">
-        <v>35</v>
+      <c r="AB57">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C58" t="s">
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>48</v>
-      </c>
-      <c r="P58">
-        <v>35</v>
+        <v>54</v>
+      </c>
+      <c r="Q58">
+        <v>35</v>
+      </c>
+      <c r="AB58">
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>49</v>
-      </c>
-      <c r="R59">
-        <v>35</v>
+        <v>55</v>
+      </c>
+      <c r="P59">
+        <v>35</v>
+      </c>
+      <c r="AB59">
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P60">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="Q60">
+        <v>18</v>
+      </c>
+      <c r="R60">
+        <v>17</v>
+      </c>
+      <c r="AC60">
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
         <v>28</v>
@@ -1968,149 +2001,257 @@
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
-      </c>
-      <c r="X61">
-        <v>11</v>
-      </c>
-      <c r="AC61">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="R61">
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P62">
-        <v>17</v>
-      </c>
-      <c r="AC62">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="R62">
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C63" t="s">
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
-      </c>
-      <c r="S63">
-        <v>12</v>
-      </c>
-      <c r="T63">
-        <v>24</v>
-      </c>
-      <c r="AC63">
-        <v>25</v>
+        <v>47</v>
+      </c>
+      <c r="P63">
+        <v>35</v>
+      </c>
+      <c r="Q63">
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
-      </c>
-      <c r="S64">
-        <v>12</v>
-      </c>
-      <c r="AC64">
-        <v>25</v>
+        <v>48</v>
+      </c>
+      <c r="P64">
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>33</v>
-      </c>
-      <c r="L65" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q65">
-        <v>35</v>
-      </c>
-      <c r="AC65">
-        <v>25</v>
+        <v>49</v>
+      </c>
+      <c r="R65">
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC66">
-        <v>25</v>
+        <v>39</v>
+      </c>
+      <c r="P66">
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y67">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="X67">
+        <v>11</v>
+      </c>
+      <c r="AC67">
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s">
+        <v>41</v>
+      </c>
+      <c r="P68">
+        <v>17</v>
+      </c>
+      <c r="AC68">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" t="s">
+        <v>42</v>
+      </c>
+      <c r="S69">
+        <v>12</v>
+      </c>
+      <c r="T69">
+        <v>24</v>
+      </c>
+      <c r="AC69">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" t="s">
+        <v>43</v>
+      </c>
+      <c r="S70">
+        <v>12</v>
+      </c>
+      <c r="AC70">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
         <v>32</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s">
+        <v>33</v>
+      </c>
+      <c r="L71" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q71">
+        <v>35</v>
+      </c>
+      <c r="AC71">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC72">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>32</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y73">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" t="s">
         <v>31</v>
       </c>
-      <c r="C68" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
         <v>37</v>
       </c>
-      <c r="Q68">
+      <c r="Q74">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91EACD8-65DF-45B3-BB3A-4CE350291369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC7D1D0-96A7-4D25-967D-26BBE11C23AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="154">
   <si>
     <t>업무일자</t>
   </si>
@@ -432,6 +432,69 @@
   </si>
   <si>
     <t>2026-04-22 06:34:35.807283</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-28 06:35:22.171911</t>
+  </si>
+  <si>
+    <t>2026-04-28 06:34:05.427642</t>
+  </si>
+  <si>
+    <t>2026-04-28 06:33:35.977526</t>
+  </si>
+  <si>
+    <t>2026-04-28 06:32:16.816790</t>
+  </si>
+  <si>
+    <t>2026-04-28 06:31:41.911875</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-27 08:33:50.278300</t>
+  </si>
+  <si>
+    <t>2026-04-27 08:33:38.739385</t>
+  </si>
+  <si>
+    <t>2026-04-27 06:34:34.639100</t>
+  </si>
+  <si>
+    <t>2026-04-27 06:31:35.895880</t>
+  </si>
+  <si>
+    <t>2026-04-27 04:10:58.735247</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-24 08:34:12.661562</t>
+  </si>
+  <si>
+    <t>2026-04-24 06:34:52.745229</t>
+  </si>
+  <si>
+    <t>2026-04-24 06:33:43.044385</t>
+  </si>
+  <si>
+    <t>2026-04-24 06:32:16.823957</t>
+  </si>
+  <si>
+    <t>2026-04-23 23:29:17.614011</t>
+  </si>
+  <si>
+    <t>22일날.프리슬림16장.전용1열30장했습니다.</t>
+  </si>
+  <si>
+    <t>2026-04-23 08:33:15.683322</t>
+  </si>
+  <si>
+    <t>2026-04-23 08:32:39.853588</t>
   </si>
 </sst>
 </file>
@@ -778,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
@@ -872,67 +935,61 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="P2">
-        <v>35</v>
-      </c>
-      <c r="AB2">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="Q2">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q3">
-        <v>18</v>
-      </c>
-      <c r="AB3">
-        <v>30</v>
+        <v>135</v>
+      </c>
+      <c r="AC3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
-      </c>
-      <c r="T4">
-        <v>24</v>
-      </c>
-      <c r="AC4">
-        <v>15</v>
+        <v>136</v>
+      </c>
+      <c r="P4">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -941,18 +998,15 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q5">
-        <v>35</v>
-      </c>
-      <c r="AC5">
-        <v>15</v>
+        <v>137</v>
+      </c>
+      <c r="R5">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -961,18 +1015,18 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="P6">
         <v>18</v>
       </c>
       <c r="Q6">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -981,43 +1035,46 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
-      </c>
-      <c r="P7">
+        <v>140</v>
+      </c>
+      <c r="Q7">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8">
-        <v>35</v>
+        <v>141</v>
+      </c>
+      <c r="P8">
+        <v>35</v>
+      </c>
+      <c r="AC8">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="P9">
+        <v>142</v>
+      </c>
+      <c r="R9">
         <v>35</v>
       </c>
       <c r="AC9">
@@ -1026,517 +1083,520 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
-      </c>
-      <c r="L10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z10">
-        <v>30</v>
+        <v>143</v>
+      </c>
+      <c r="P10">
+        <v>35</v>
+      </c>
+      <c r="R10">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB11">
-        <v>60</v>
+        <v>144</v>
+      </c>
+      <c r="AC11">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q12">
+        <v>146</v>
+      </c>
+      <c r="R12">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q13">
+        <v>147</v>
+      </c>
+      <c r="P13">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="P14">
-        <v>35</v>
-      </c>
-      <c r="S14">
-        <v>12</v>
-      </c>
-      <c r="Y14">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="Q14">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
-      </c>
-      <c r="P15">
-        <v>35</v>
+        <v>149</v>
+      </c>
+      <c r="R15">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>150</v>
+      </c>
+      <c r="N16" t="s">
+        <v>151</v>
       </c>
       <c r="P16">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q16">
+        <v>17</v>
+      </c>
+      <c r="R16">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
-      </c>
-      <c r="L17" t="s">
-        <v>124</v>
-      </c>
-      <c r="P17">
-        <v>18</v>
-      </c>
-      <c r="Q17">
-        <v>35</v>
+        <v>152</v>
+      </c>
+      <c r="Z17">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
-      </c>
-      <c r="L18" t="s">
-        <v>98</v>
-      </c>
-      <c r="P18">
-        <v>35</v>
-      </c>
-      <c r="AA18">
+        <v>153</v>
+      </c>
+      <c r="AC18">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q19">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="P19">
+        <v>35</v>
+      </c>
+      <c r="AB19">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC20">
-        <v>25</v>
+        <v>127</v>
+      </c>
+      <c r="Q20">
+        <v>18</v>
+      </c>
+      <c r="AB20">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB21">
-        <v>59</v>
+        <v>129</v>
+      </c>
+      <c r="T21">
+        <v>24</v>
       </c>
       <c r="AC21">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>130</v>
+      </c>
+      <c r="Q22">
+        <v>35</v>
       </c>
       <c r="AC22">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB23">
-        <v>30</v>
+        <v>131</v>
+      </c>
+      <c r="P23">
+        <v>18</v>
+      </c>
+      <c r="Q23">
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC24">
-        <v>25</v>
+        <v>132</v>
+      </c>
+      <c r="P24">
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB25">
-        <v>30</v>
-      </c>
-      <c r="AC25">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="Q25">
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
-      </c>
-      <c r="L26" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB26">
-        <v>30</v>
+        <v>114</v>
+      </c>
+      <c r="P26">
+        <v>35</v>
+      </c>
+      <c r="AC26">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC27">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="L27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z27">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC28">
-        <v>25</v>
+        <v>116</v>
+      </c>
+      <c r="AB28">
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
-      </c>
-      <c r="P29">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Q29">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB30">
-        <v>30</v>
-      </c>
-      <c r="AC30">
-        <v>25</v>
+        <v>119</v>
+      </c>
+      <c r="Q30">
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC31">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P31">
+        <v>35</v>
+      </c>
+      <c r="S31">
+        <v>12</v>
+      </c>
+      <c r="Y31">
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="P32">
-        <v>18</v>
-      </c>
-      <c r="AC32">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB33">
-        <v>30</v>
+        <v>122</v>
+      </c>
+      <c r="P33">
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>123</v>
+      </c>
+      <c r="L34" t="s">
+        <v>124</v>
       </c>
       <c r="P34">
         <v>18</v>
       </c>
       <c r="Q34">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="L35" t="s">
+        <v>98</v>
       </c>
       <c r="P35">
         <v>35</v>
+      </c>
+      <c r="AA35">
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
-      </c>
-      <c r="L36" t="s">
-        <v>93</v>
-      </c>
-      <c r="P36">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="Q36">
-        <v>37</v>
-      </c>
-      <c r="R36">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
         <v>30</v>
@@ -1545,35 +1605,35 @@
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
-      </c>
-      <c r="P37">
-        <v>18</v>
-      </c>
-      <c r="Q37">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="AC37">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q38">
-        <v>35</v>
+        <v>102</v>
+      </c>
+      <c r="AB38">
+        <v>59</v>
+      </c>
+      <c r="AC38">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
         <v>28</v>
@@ -1582,47 +1642,41 @@
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
-      </c>
-      <c r="X39">
-        <v>15</v>
+        <v>103</v>
+      </c>
+      <c r="AC39">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
-      </c>
-      <c r="P40">
-        <v>18</v>
-      </c>
-      <c r="Q40">
-        <v>52</v>
+        <v>104</v>
+      </c>
+      <c r="AB40">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q41">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="AC41">
         <v>25</v>
@@ -1630,41 +1684,47 @@
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
-      </c>
-      <c r="P42">
-        <v>35</v>
+        <v>106</v>
+      </c>
+      <c r="AB42">
+        <v>30</v>
+      </c>
+      <c r="AC42">
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC43">
-        <v>25</v>
+        <v>108</v>
+      </c>
+      <c r="L43" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB43">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
         <v>29</v>
@@ -1673,64 +1733,64 @@
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC44">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>76</v>
-      </c>
-      <c r="P45">
-        <v>18</v>
+        <v>111</v>
+      </c>
+      <c r="AC45">
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB46">
-        <v>46</v>
-      </c>
-      <c r="AC46">
-        <v>25</v>
+        <v>84</v>
+      </c>
+      <c r="P46">
+        <v>35</v>
+      </c>
+      <c r="Q46">
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
-      </c>
-      <c r="L47" t="s">
-        <v>62</v>
+        <v>85</v>
+      </c>
+      <c r="AB47">
+        <v>30</v>
       </c>
       <c r="AC47">
         <v>25</v>
@@ -1738,19 +1798,16 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB48">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="AC48">
         <v>25</v>
@@ -1758,19 +1815,19 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="P49">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="AC49">
         <v>25</v>
@@ -1778,24 +1835,24 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC50">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="AB50">
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B51" t="s">
         <v>28</v>
@@ -1804,32 +1861,35 @@
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA51">
-        <v>15</v>
+        <v>90</v>
+      </c>
+      <c r="P51">
+        <v>18</v>
+      </c>
+      <c r="Q51">
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB52">
-        <v>30</v>
+        <v>91</v>
+      </c>
+      <c r="P52">
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
@@ -1838,18 +1898,24 @@
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="L53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA53">
-        <v>11</v>
+        <v>93</v>
+      </c>
+      <c r="P53">
+        <v>17</v>
+      </c>
+      <c r="Q53">
+        <v>37</v>
+      </c>
+      <c r="R53">
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
         <v>30</v>
@@ -1858,75 +1924,72 @@
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB54">
-        <v>30</v>
+        <v>94</v>
+      </c>
+      <c r="P54">
+        <v>18</v>
+      </c>
+      <c r="Q54">
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB55">
-        <v>30</v>
+        <v>95</v>
+      </c>
+      <c r="Q55">
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
-      </c>
-      <c r="L56" t="s">
-        <v>52</v>
-      </c>
-      <c r="R56">
-        <v>35</v>
-      </c>
-      <c r="AB56">
-        <v>30</v>
+        <v>79</v>
+      </c>
+      <c r="X56">
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="P57">
-        <v>35</v>
-      </c>
-      <c r="AB57">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="Q57">
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
         <v>31</v>
@@ -1935,18 +1998,18 @@
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="Q58">
-        <v>35</v>
-      </c>
-      <c r="AB58">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="AC58">
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
@@ -1955,164 +2018,155 @@
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="P59">
         <v>35</v>
-      </c>
-      <c r="AB59">
-        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
-      </c>
-      <c r="P60">
-        <v>17</v>
-      </c>
-      <c r="Q60">
-        <v>18</v>
-      </c>
-      <c r="R60">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="AC60">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>45</v>
-      </c>
-      <c r="R61">
-        <v>35</v>
+        <v>75</v>
+      </c>
+      <c r="AC61">
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C62" t="s">
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="P62">
-        <v>35</v>
-      </c>
-      <c r="R62">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C63" t="s">
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>47</v>
-      </c>
-      <c r="P63">
-        <v>35</v>
-      </c>
-      <c r="Q63">
-        <v>35</v>
+        <v>77</v>
+      </c>
+      <c r="AB63">
+        <v>46</v>
+      </c>
+      <c r="AC63">
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>48</v>
-      </c>
-      <c r="P64">
-        <v>35</v>
+        <v>61</v>
+      </c>
+      <c r="L64" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC64">
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
-      </c>
-      <c r="R65">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="AB65">
+        <v>21</v>
+      </c>
+      <c r="AC65">
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P66">
         <v>35</v>
+      </c>
+      <c r="AC66">
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>40</v>
-      </c>
-      <c r="X67">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AC67">
         <v>25</v>
@@ -2120,27 +2174,24 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
         <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>41</v>
-      </c>
-      <c r="P68">
-        <v>17</v>
-      </c>
-      <c r="AC68">
-        <v>25</v>
+        <v>67</v>
+      </c>
+      <c r="AA68">
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
         <v>29</v>
@@ -2149,109 +2200,437 @@
         <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>42</v>
-      </c>
-      <c r="S69">
-        <v>12</v>
-      </c>
-      <c r="T69">
-        <v>24</v>
-      </c>
-      <c r="AC69">
-        <v>25</v>
+        <v>68</v>
+      </c>
+      <c r="AB69">
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
-      </c>
-      <c r="S70">
-        <v>12</v>
-      </c>
-      <c r="AC70">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="L70" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA70">
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
         <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>33</v>
-      </c>
-      <c r="L71" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q71">
-        <v>35</v>
-      </c>
-      <c r="AC71">
-        <v>25</v>
+        <v>71</v>
+      </c>
+      <c r="AB71">
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
         <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC72">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="AB72">
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
         <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y73">
+        <v>51</v>
+      </c>
+      <c r="L73" t="s">
+        <v>52</v>
+      </c>
+      <c r="R73">
+        <v>35</v>
+      </c>
+      <c r="AB73">
         <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
+        <v>50</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
+        <v>53</v>
+      </c>
+      <c r="P74">
+        <v>35</v>
+      </c>
+      <c r="AB74">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>50</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q75">
+        <v>35</v>
+      </c>
+      <c r="AB75">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>50</v>
+      </c>
+      <c r="B76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" t="s">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s">
+        <v>55</v>
+      </c>
+      <c r="P76">
+        <v>35</v>
+      </c>
+      <c r="AB76">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s">
+        <v>56</v>
+      </c>
+      <c r="P77">
+        <v>17</v>
+      </c>
+      <c r="Q77">
+        <v>18</v>
+      </c>
+      <c r="R77">
+        <v>17</v>
+      </c>
+      <c r="AC77">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>45</v>
+      </c>
+      <c r="R78">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" t="s">
+        <v>46</v>
+      </c>
+      <c r="P79">
+        <v>35</v>
+      </c>
+      <c r="R79">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s">
+        <v>47</v>
+      </c>
+      <c r="P80">
+        <v>35</v>
+      </c>
+      <c r="Q80">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" t="s">
+        <v>48</v>
+      </c>
+      <c r="P81">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" t="s">
+        <v>49</v>
+      </c>
+      <c r="R82">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" t="s">
+        <v>39</v>
+      </c>
+      <c r="P83">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" t="s">
+        <v>40</v>
+      </c>
+      <c r="X84">
+        <v>11</v>
+      </c>
+      <c r="AC84">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>38</v>
+      </c>
+      <c r="B85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="P85">
+        <v>17</v>
+      </c>
+      <c r="AC85">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" t="s">
+        <v>42</v>
+      </c>
+      <c r="S86">
+        <v>12</v>
+      </c>
+      <c r="T86">
+        <v>24</v>
+      </c>
+      <c r="AC86">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>38</v>
+      </c>
+      <c r="B87" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" t="s">
+        <v>43</v>
+      </c>
+      <c r="S87">
+        <v>12</v>
+      </c>
+      <c r="AC87">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
         <v>32</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" t="s">
+        <v>33</v>
+      </c>
+      <c r="L88" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q88">
+        <v>35</v>
+      </c>
+      <c r="AC88">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>27</v>
+      </c>
+      <c r="D89" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC89">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" t="s">
+        <v>30</v>
+      </c>
+      <c r="C90" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y90">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>32</v>
+      </c>
+      <c r="B91" t="s">
         <v>31</v>
       </c>
-      <c r="C74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C91" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" t="s">
         <v>37</v>
       </c>
-      <c r="Q74">
+      <c r="Q91">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC7D1D0-96A7-4D25-967D-26BBE11C23AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D410E6E-5508-4353-A58C-3F02AEC7D65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="167">
   <si>
     <t>업무일자</t>
   </si>
@@ -495,6 +495,45 @@
   </si>
   <si>
     <t>2026-04-23 08:32:39.853588</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-30 08:57:26.654080</t>
+  </si>
+  <si>
+    <t>2026-04-30 08:33:27.833416</t>
+  </si>
+  <si>
+    <t>2026-04-30 06:35:35.800543</t>
+  </si>
+  <si>
+    <t>2026-04-30 06:33:37.066664</t>
+  </si>
+  <si>
+    <t>2026-04-30 06:31:00.048983</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-29 08:33:16.634458</t>
+  </si>
+  <si>
+    <t>2026-04-29 08:31:14.879502</t>
+  </si>
+  <si>
+    <t>포르쉐.레드.하는~중</t>
+  </si>
+  <si>
+    <t>2026-04-29 08:30:47.519101</t>
+  </si>
+  <si>
+    <t>2026-04-29 06:35:19.982061</t>
+  </si>
+  <si>
+    <t>2026-04-29 06:33:27.503811</t>
   </si>
 </sst>
 </file>
@@ -841,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
@@ -935,27 +974,27 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="P2">
-        <v>18</v>
-      </c>
-      <c r="Q2">
-        <v>17</v>
+        <v>155</v>
+      </c>
+      <c r="AB2">
+        <v>30</v>
+      </c>
+      <c r="AC2">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -964,32 +1003,35 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC3">
-        <v>9</v>
+        <v>156</v>
+      </c>
+      <c r="AB3">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="P4">
-        <v>35</v>
+        <v>157</v>
+      </c>
+      <c r="X4">
+        <v>15</v>
+      </c>
+      <c r="AB4">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -998,15 +1040,18 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
-      </c>
-      <c r="R5">
-        <v>53</v>
+        <v>158</v>
+      </c>
+      <c r="Y5">
+        <v>26</v>
+      </c>
+      <c r="AB5">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1015,95 +1060,95 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P6">
-        <v>18</v>
-      </c>
-      <c r="Q6">
-        <v>17</v>
+        <v>159</v>
+      </c>
+      <c r="AB6">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q7">
-        <v>35</v>
+        <v>161</v>
+      </c>
+      <c r="U7">
+        <v>30</v>
+      </c>
+      <c r="AC7">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>162</v>
+      </c>
+      <c r="L8" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
         <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="P8">
-        <v>35</v>
-      </c>
-      <c r="AC8">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="R9">
         <v>35</v>
       </c>
       <c r="AC9">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="P10">
         <v>35</v>
-      </c>
-      <c r="R10">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1112,49 +1157,55 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC11">
-        <v>25</v>
+        <v>166</v>
+      </c>
+      <c r="Q11">
+        <v>18</v>
+      </c>
+      <c r="R11">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
-      </c>
-      <c r="R12">
-        <v>35</v>
+        <v>134</v>
+      </c>
+      <c r="P12">
+        <v>18</v>
+      </c>
+      <c r="Q12">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
-      </c>
-      <c r="P13">
-        <v>35</v>
+        <v>135</v>
+      </c>
+      <c r="AC13">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1163,47 +1214,41 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="P14">
-        <v>18</v>
-      </c>
-      <c r="Q14">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="R15">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
-      </c>
-      <c r="N16" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="P16">
         <v>18</v>
@@ -1211,147 +1256,138 @@
       <c r="Q16">
         <v>17</v>
       </c>
-      <c r="R16">
-        <v>18</v>
-      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z17">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="Q17">
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>141</v>
+      </c>
+      <c r="P18">
+        <v>35</v>
       </c>
       <c r="AC18">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
-      </c>
-      <c r="P19">
-        <v>35</v>
-      </c>
-      <c r="AB19">
-        <v>38</v>
+        <v>142</v>
+      </c>
+      <c r="R19">
+        <v>35</v>
+      </c>
+      <c r="AC19">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q20">
-        <v>18</v>
-      </c>
-      <c r="AB20">
-        <v>30</v>
+        <v>143</v>
+      </c>
+      <c r="P20">
+        <v>35</v>
+      </c>
+      <c r="R20">
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="T21">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="AC21">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q22">
-        <v>35</v>
-      </c>
-      <c r="AC22">
-        <v>15</v>
+        <v>146</v>
+      </c>
+      <c r="R22">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="P23">
-        <v>18</v>
-      </c>
-      <c r="Q23">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1360,64 +1396,70 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="P24">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q24">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q25">
-        <v>35</v>
+        <v>149</v>
+      </c>
+      <c r="R25">
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>150</v>
+      </c>
+      <c r="N26" t="s">
+        <v>151</v>
       </c>
       <c r="P26">
-        <v>35</v>
-      </c>
-      <c r="AC26">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="Q26">
+        <v>17</v>
+      </c>
+      <c r="R26">
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
-      </c>
-      <c r="L27" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="Z27">
         <v>30</v>
@@ -1425,372 +1467,378 @@
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB28">
-        <v>60</v>
+        <v>153</v>
+      </c>
+      <c r="AC28">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q29">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="P29">
+        <v>35</v>
+      </c>
+      <c r="AB29">
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="Q30">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="AB30">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="P31">
-        <v>35</v>
-      </c>
-      <c r="S31">
-        <v>12</v>
-      </c>
-      <c r="Y31">
-        <v>16</v>
+        <v>129</v>
+      </c>
+      <c r="T31">
+        <v>24</v>
+      </c>
+      <c r="AC31">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="P32">
-        <v>35</v>
+        <v>130</v>
+      </c>
+      <c r="Q32">
+        <v>35</v>
+      </c>
+      <c r="AC32">
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="P33">
+        <v>18</v>
+      </c>
+      <c r="Q33">
         <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="L34" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="P34">
-        <v>18</v>
-      </c>
-      <c r="Q34">
         <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
-      </c>
-      <c r="L35" t="s">
-        <v>98</v>
-      </c>
-      <c r="P35">
-        <v>35</v>
-      </c>
-      <c r="AA35">
-        <v>15</v>
+        <v>113</v>
+      </c>
+      <c r="Q35">
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q36">
-        <v>35</v>
+        <v>114</v>
+      </c>
+      <c r="P36">
+        <v>35</v>
+      </c>
+      <c r="AC36">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC37">
-        <v>25</v>
+        <v>115</v>
+      </c>
+      <c r="L37" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z37">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="AB38">
-        <v>59</v>
-      </c>
-      <c r="AC38">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC39">
-        <v>25</v>
+        <v>117</v>
+      </c>
+      <c r="Q39">
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB40">
-        <v>30</v>
+        <v>119</v>
+      </c>
+      <c r="Q40">
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC41">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P41">
+        <v>35</v>
+      </c>
+      <c r="S41">
+        <v>12</v>
+      </c>
+      <c r="Y41">
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB42">
-        <v>30</v>
-      </c>
-      <c r="AC42">
-        <v>25</v>
+        <v>121</v>
+      </c>
+      <c r="P42">
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
-      </c>
-      <c r="L43" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB43">
-        <v>30</v>
+        <v>122</v>
+      </c>
+      <c r="P43">
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC44">
-        <v>15</v>
+        <v>123</v>
+      </c>
+      <c r="L44" t="s">
+        <v>124</v>
+      </c>
+      <c r="P44">
+        <v>18</v>
+      </c>
+      <c r="Q44">
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC45">
-        <v>25</v>
+        <v>97</v>
+      </c>
+      <c r="L45" t="s">
+        <v>98</v>
+      </c>
+      <c r="P45">
+        <v>35</v>
+      </c>
+      <c r="AA45">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
-      </c>
-      <c r="P46">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="Q46">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB47">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AC47">
         <v>25</v>
@@ -1798,7 +1846,7 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
         <v>31</v>
@@ -1807,7 +1855,10 @@
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
+        <v>102</v>
+      </c>
+      <c r="AB48">
+        <v>59</v>
       </c>
       <c r="AC48">
         <v>25</v>
@@ -1815,19 +1866,16 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
-      </c>
-      <c r="P49">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="AC49">
         <v>25</v>
@@ -1835,7 +1883,7 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
         <v>30</v>
@@ -1844,7 +1892,7 @@
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="AB50">
         <v>30</v>
@@ -1852,44 +1900,44 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
-      </c>
-      <c r="P51">
-        <v>18</v>
-      </c>
-      <c r="Q51">
-        <v>17</v>
+        <v>105</v>
+      </c>
+      <c r="AC51">
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
-      </c>
-      <c r="P52">
-        <v>35</v>
+        <v>106</v>
+      </c>
+      <c r="AB52">
+        <v>30</v>
+      </c>
+      <c r="AC52">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
@@ -1898,61 +1946,52 @@
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s">
-        <v>93</v>
-      </c>
-      <c r="P53">
-        <v>17</v>
-      </c>
-      <c r="Q53">
-        <v>37</v>
-      </c>
-      <c r="R53">
-        <v>18</v>
+        <v>109</v>
+      </c>
+      <c r="AB53">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>94</v>
-      </c>
-      <c r="P54">
-        <v>18</v>
-      </c>
-      <c r="Q54">
-        <v>17</v>
+        <v>110</v>
+      </c>
+      <c r="AC54">
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q55">
-        <v>35</v>
+        <v>111</v>
+      </c>
+      <c r="AC55">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
         <v>28</v>
@@ -1961,15 +2000,18 @@
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>79</v>
-      </c>
-      <c r="X56">
-        <v>15</v>
+        <v>84</v>
+      </c>
+      <c r="P56">
+        <v>35</v>
+      </c>
+      <c r="Q56">
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s">
         <v>29</v>
@@ -1978,18 +2020,18 @@
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
-      </c>
-      <c r="P57">
-        <v>18</v>
-      </c>
-      <c r="Q57">
-        <v>52</v>
+        <v>85</v>
+      </c>
+      <c r="AB57">
+        <v>30</v>
+      </c>
+      <c r="AC57">
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
         <v>31</v>
@@ -1998,10 +2040,7 @@
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q58">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="AC58">
         <v>25</v>
@@ -2009,58 +2048,64 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="P59">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="AC59">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC60">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="AB60">
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC61">
-        <v>25</v>
+        <v>90</v>
+      </c>
+      <c r="P61">
+        <v>18</v>
+      </c>
+      <c r="Q61">
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B62" t="s">
         <v>31</v>
@@ -2069,183 +2114,186 @@
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="P62">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB63">
-        <v>46</v>
-      </c>
-      <c r="AC63">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="L63" t="s">
+        <v>93</v>
+      </c>
+      <c r="P63">
+        <v>17</v>
+      </c>
+      <c r="Q63">
+        <v>37</v>
+      </c>
+      <c r="R63">
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
-      </c>
-      <c r="L64" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC64">
-        <v>25</v>
+        <v>94</v>
+      </c>
+      <c r="P64">
+        <v>18</v>
+      </c>
+      <c r="Q64">
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB65">
-        <v>21</v>
-      </c>
-      <c r="AC65">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="Q65">
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>64</v>
-      </c>
-      <c r="P66">
-        <v>35</v>
-      </c>
-      <c r="AC66">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="X66">
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC67">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="P67">
+        <v>18</v>
+      </c>
+      <c r="Q67">
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
         <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA68">
-        <v>15</v>
+        <v>81</v>
+      </c>
+      <c r="Q68">
+        <v>17</v>
+      </c>
+      <c r="AC68">
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB69">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P69">
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>69</v>
-      </c>
-      <c r="L70" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA70">
-        <v>11</v>
+        <v>74</v>
+      </c>
+      <c r="AC70">
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
         <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB71">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="AC71">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
         <v>31</v>
@@ -2254,124 +2302,112 @@
         <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB72">
-        <v>30</v>
+        <v>76</v>
+      </c>
+      <c r="P72">
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
         <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
-      </c>
-      <c r="L73" t="s">
-        <v>52</v>
-      </c>
-      <c r="R73">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="AB73">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="AC73">
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
         <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
-      </c>
-      <c r="P74">
-        <v>35</v>
-      </c>
-      <c r="AB74">
-        <v>30</v>
+        <v>61</v>
+      </c>
+      <c r="L74" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC74">
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
         <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q75">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AB75">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="AC75">
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
         <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P76">
         <v>35</v>
       </c>
-      <c r="AB76">
-        <v>30</v>
+      <c r="AC76">
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C77" t="s">
         <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
-      </c>
-      <c r="P77">
-        <v>17</v>
-      </c>
-      <c r="Q77">
-        <v>18</v>
-      </c>
-      <c r="R77">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="AC77">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
         <v>28</v>
@@ -2380,55 +2416,52 @@
         <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>45</v>
-      </c>
-      <c r="R78">
-        <v>35</v>
+        <v>67</v>
+      </c>
+      <c r="AA78">
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
         <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>46</v>
-      </c>
-      <c r="P79">
-        <v>35</v>
-      </c>
-      <c r="R79">
-        <v>35</v>
+        <v>68</v>
+      </c>
+      <c r="AB79">
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C80" t="s">
         <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>47</v>
-      </c>
-      <c r="P80">
-        <v>35</v>
-      </c>
-      <c r="Q80">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="L80" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA80">
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
         <v>30</v>
@@ -2437,32 +2470,32 @@
         <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>48</v>
-      </c>
-      <c r="P81">
-        <v>35</v>
+        <v>71</v>
+      </c>
+      <c r="AB81">
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C82" t="s">
         <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>49</v>
-      </c>
-      <c r="R82">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="AB82">
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B83" t="s">
         <v>26</v>
@@ -2471,15 +2504,21 @@
         <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>39</v>
-      </c>
-      <c r="P83">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="L83" t="s">
+        <v>52</v>
+      </c>
+      <c r="R83">
+        <v>35</v>
+      </c>
+      <c r="AB83">
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B84" t="s">
         <v>28</v>
@@ -2488,149 +2527,343 @@
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
-      </c>
-      <c r="X84">
-        <v>11</v>
-      </c>
-      <c r="AC84">
-        <v>25</v>
+        <v>53</v>
+      </c>
+      <c r="P84">
+        <v>35</v>
+      </c>
+      <c r="AB84">
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C85" t="s">
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>41</v>
-      </c>
-      <c r="P85">
-        <v>17</v>
-      </c>
-      <c r="AC85">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="Q85">
+        <v>35</v>
+      </c>
+      <c r="AB85">
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C86" t="s">
         <v>27</v>
       </c>
       <c r="D86" t="s">
-        <v>42</v>
-      </c>
-      <c r="S86">
-        <v>12</v>
-      </c>
-      <c r="T86">
-        <v>24</v>
-      </c>
-      <c r="AC86">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="P86">
+        <v>35</v>
+      </c>
+      <c r="AB86">
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C87" t="s">
         <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>43</v>
-      </c>
-      <c r="S87">
-        <v>12</v>
+        <v>56</v>
+      </c>
+      <c r="P87">
+        <v>17</v>
+      </c>
+      <c r="Q87">
+        <v>18</v>
+      </c>
+      <c r="R87">
+        <v>17</v>
       </c>
       <c r="AC87">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
         <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>33</v>
-      </c>
-      <c r="L88" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q88">
-        <v>35</v>
-      </c>
-      <c r="AC88">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="R88">
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C89" t="s">
         <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC89">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="P89">
+        <v>35</v>
+      </c>
+      <c r="R89">
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C90" t="s">
         <v>27</v>
       </c>
       <c r="D90" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y90">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="P90">
+        <v>35</v>
+      </c>
+      <c r="Q90">
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B91" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" t="s">
+        <v>48</v>
+      </c>
+      <c r="P91">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" t="s">
+        <v>49</v>
+      </c>
+      <c r="R92">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" t="s">
+        <v>39</v>
+      </c>
+      <c r="P93">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" t="s">
+        <v>28</v>
+      </c>
+      <c r="C94" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" t="s">
+        <v>40</v>
+      </c>
+      <c r="X94">
+        <v>11</v>
+      </c>
+      <c r="AC94">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>38</v>
+      </c>
+      <c r="B95" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" t="s">
+        <v>41</v>
+      </c>
+      <c r="P95">
+        <v>17</v>
+      </c>
+      <c r="AC95">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>38</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" t="s">
+        <v>27</v>
+      </c>
+      <c r="D96" t="s">
+        <v>42</v>
+      </c>
+      <c r="S96">
+        <v>12</v>
+      </c>
+      <c r="T96">
+        <v>24</v>
+      </c>
+      <c r="AC96">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>38</v>
+      </c>
+      <c r="B97" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" t="s">
+        <v>27</v>
+      </c>
+      <c r="D97" t="s">
+        <v>43</v>
+      </c>
+      <c r="S97">
+        <v>12</v>
+      </c>
+      <c r="AC97">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
         <v>32</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>27</v>
+      </c>
+      <c r="D98" t="s">
+        <v>33</v>
+      </c>
+      <c r="L98" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q98">
+        <v>35</v>
+      </c>
+      <c r="AC98">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>27</v>
+      </c>
+      <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC99">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" t="s">
+        <v>30</v>
+      </c>
+      <c r="C100" t="s">
+        <v>27</v>
+      </c>
+      <c r="D100" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y100">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" t="s">
         <v>31</v>
       </c>
-      <c r="C91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C101" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" t="s">
         <v>37</v>
       </c>
-      <c r="Q91">
+      <c r="Q101">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D410E6E-5508-4353-A58C-3F02AEC7D65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31C7293-05B8-42B6-B0EB-1309BD144638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="199">
   <si>
     <t>업무일자</t>
   </si>
@@ -534,6 +534,102 @@
   </si>
   <si>
     <t>2026-04-29 06:33:27.503811</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-11 21:12:49.914598</t>
+  </si>
+  <si>
+    <t>2026-05-11 08:33:18.904830</t>
+  </si>
+  <si>
+    <t>2026-05-11 06:38:39.776246</t>
+  </si>
+  <si>
+    <t>2026-05-11 06:36:07.494491</t>
+  </si>
+  <si>
+    <t>2026-05-11 06:34:04.054096</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-09 01:11:16.346716</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-08 06:34:48.421814</t>
+  </si>
+  <si>
+    <t>헤드(카키)하는~중</t>
+  </si>
+  <si>
+    <t>2026-05-08 06:31:40.401521</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-07 10:10:05.624920</t>
+  </si>
+  <si>
+    <t>2026-05-07 08:33:16.922619</t>
+  </si>
+  <si>
+    <t>2026-05-07 08:32:45.383228</t>
+  </si>
+  <si>
+    <t>2026-05-07 08:18:35.115216</t>
+  </si>
+  <si>
+    <t>2026-05-07 06:35:25.287097</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-06 08:32:47.718659</t>
+  </si>
+  <si>
+    <t>2026-05-06 06:36:37.592573</t>
+  </si>
+  <si>
+    <t>백커버 (코튼)하는~중</t>
+  </si>
+  <si>
+    <t>2026-05-06 06:33:47.702234</t>
+  </si>
+  <si>
+    <t>2026-05-06 06:32:48.609986</t>
+  </si>
+  <si>
+    <t>2026-05-06 06:31:33.877192</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-04 08:33:39.117247</t>
+  </si>
+  <si>
+    <t>전용1열하는~중</t>
+  </si>
+  <si>
+    <t>2026-05-04 08:33:30.503761</t>
+  </si>
+  <si>
+    <t>2026-05-04 08:33:02.491771</t>
+  </si>
+  <si>
+    <t>2026-05-04 06:34:40.189591</t>
+  </si>
+  <si>
+    <t>2026-05-04 06:33:20.681726</t>
   </si>
 </sst>
 </file>
@@ -576,8 +672,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -880,8 +977,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC124"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -974,27 +1074,24 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB2">
-        <v>30</v>
-      </c>
-      <c r="AC2">
-        <v>15</v>
+        <v>168</v>
+      </c>
+      <c r="P2">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -1003,15 +1100,15 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB3">
-        <v>60</v>
+        <v>169</v>
+      </c>
+      <c r="Q3">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1020,38 +1117,41 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
-      </c>
-      <c r="X4">
-        <v>15</v>
-      </c>
-      <c r="AB4">
+        <v>170</v>
+      </c>
+      <c r="Q4">
+        <v>18</v>
+      </c>
+      <c r="R4">
+        <v>17</v>
+      </c>
+      <c r="Z4">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y5">
-        <v>26</v>
+        <v>171</v>
+      </c>
+      <c r="P5">
+        <v>18</v>
       </c>
       <c r="AB5">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1060,35 +1160,35 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB6">
-        <v>60</v>
+        <v>172</v>
+      </c>
+      <c r="P6">
+        <v>18</v>
+      </c>
+      <c r="Q6">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
-      </c>
-      <c r="U7">
-        <v>30</v>
+        <v>174</v>
       </c>
       <c r="AC7">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1097,21 +1197,21 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="L8" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="AB8">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1120,92 +1220,101 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
-      </c>
-      <c r="R9">
-        <v>35</v>
-      </c>
-      <c r="AC9">
-        <v>15</v>
+        <v>178</v>
+      </c>
+      <c r="P9">
+        <v>18</v>
+      </c>
+      <c r="S9">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="P10">
-        <v>35</v>
+        <v>180</v>
+      </c>
+      <c r="Q10">
+        <v>17</v>
+      </c>
+      <c r="AB10">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q11">
-        <v>18</v>
-      </c>
-      <c r="R11">
-        <v>17</v>
+        <v>181</v>
+      </c>
+      <c r="AB11">
+        <v>30</v>
+      </c>
+      <c r="AC11">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="P12">
+        <v>17</v>
+      </c>
+      <c r="Q12">
         <v>18</v>
       </c>
-      <c r="Q12">
-        <v>17</v>
+      <c r="AB12">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>183</v>
+      </c>
+      <c r="AB13">
+        <v>30</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1214,52 +1323,52 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="P14">
-        <v>35</v>
+        <v>184</v>
+      </c>
+      <c r="AB14">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="R15">
-        <v>53</v>
+        <v>186</v>
+      </c>
+      <c r="AC15">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="P16">
-        <v>18</v>
-      </c>
-      <c r="Q16">
-        <v>17</v>
+        <v>187</v>
+      </c>
+      <c r="L16" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z16">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -1268,294 +1377,294 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q17">
-        <v>35</v>
+        <v>189</v>
+      </c>
+      <c r="AC17">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="P18">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q18">
+        <v>17</v>
       </c>
       <c r="AC18">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
-      </c>
-      <c r="R19">
-        <v>35</v>
-      </c>
-      <c r="AC19">
-        <v>25</v>
+        <v>191</v>
+      </c>
+      <c r="P19">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>193</v>
+      </c>
+      <c r="L20" t="s">
+        <v>194</v>
       </c>
       <c r="P20">
         <v>35</v>
       </c>
-      <c r="R20">
-        <v>16</v>
+      <c r="AB20">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC21">
-        <v>25</v>
+        <v>195</v>
+      </c>
+      <c r="Z21">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
-      </c>
-      <c r="R22">
-        <v>35</v>
+        <v>196</v>
+      </c>
+      <c r="AC22">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
-      </c>
-      <c r="P23">
-        <v>35</v>
+        <v>197</v>
+      </c>
+      <c r="AC23">
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
-      </c>
-      <c r="P24">
-        <v>18</v>
-      </c>
-      <c r="Q24">
-        <v>17</v>
+        <v>198</v>
+      </c>
+      <c r="AB24">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
-      </c>
-      <c r="R25">
-        <v>18</v>
+        <v>155</v>
+      </c>
+      <c r="AB25">
+        <v>30</v>
+      </c>
+      <c r="AC25">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
-      </c>
-      <c r="N26" t="s">
-        <v>151</v>
-      </c>
-      <c r="P26">
-        <v>18</v>
-      </c>
-      <c r="Q26">
-        <v>17</v>
-      </c>
-      <c r="R26">
-        <v>18</v>
+        <v>156</v>
+      </c>
+      <c r="AB26">
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z27">
+        <v>157</v>
+      </c>
+      <c r="X27">
+        <v>15</v>
+      </c>
+      <c r="AB27">
         <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
-      </c>
-      <c r="AC28">
-        <v>15</v>
+        <v>158</v>
+      </c>
+      <c r="Y28">
+        <v>26</v>
+      </c>
+      <c r="AB28">
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
-      </c>
-      <c r="P29">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="AB29">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q30">
-        <v>18</v>
-      </c>
-      <c r="AB30">
-        <v>30</v>
+        <v>161</v>
+      </c>
+      <c r="U30">
+        <v>30</v>
+      </c>
+      <c r="AC30">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>162</v>
+      </c>
+      <c r="L31" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
         <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" t="s">
-        <v>129</v>
-      </c>
-      <c r="T31">
-        <v>24</v>
-      </c>
-      <c r="AC31">
-        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q32">
+        <v>164</v>
+      </c>
+      <c r="R32">
         <v>35</v>
       </c>
       <c r="AC32">
@@ -1564,61 +1673,64 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="P33">
-        <v>18</v>
-      </c>
-      <c r="Q33">
         <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
-      </c>
-      <c r="P34">
-        <v>35</v>
+        <v>166</v>
+      </c>
+      <c r="Q34">
+        <v>18</v>
+      </c>
+      <c r="R34">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>134</v>
+      </c>
+      <c r="P35">
+        <v>18</v>
       </c>
       <c r="Q35">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s">
         <v>28</v>
@@ -1627,55 +1739,49 @@
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
-      </c>
-      <c r="P36">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="AC36">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
-      </c>
-      <c r="L37" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z37">
-        <v>30</v>
+        <v>136</v>
+      </c>
+      <c r="P37">
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB38">
-        <v>60</v>
+        <v>137</v>
+      </c>
+      <c r="R38">
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s">
         <v>29</v>
@@ -1684,24 +1790,27 @@
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>138</v>
+      </c>
+      <c r="P39">
+        <v>18</v>
       </c>
       <c r="Q39">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="Q40">
         <v>35</v>
@@ -1709,127 +1818,118 @@
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="P41">
         <v>35</v>
       </c>
-      <c r="S41">
-        <v>12</v>
-      </c>
-      <c r="Y41">
+      <c r="AC41">
         <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
-      </c>
-      <c r="P42">
-        <v>35</v>
+        <v>142</v>
+      </c>
+      <c r="R42">
+        <v>35</v>
+      </c>
+      <c r="AC42">
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="P43">
         <v>35</v>
+      </c>
+      <c r="R43">
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="L44" t="s">
-        <v>124</v>
-      </c>
-      <c r="P44">
-        <v>18</v>
-      </c>
-      <c r="Q44">
-        <v>35</v>
+        <v>144</v>
+      </c>
+      <c r="AC44">
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
-      </c>
-      <c r="L45" t="s">
-        <v>98</v>
-      </c>
-      <c r="P45">
-        <v>35</v>
-      </c>
-      <c r="AA45">
-        <v>15</v>
+        <v>146</v>
+      </c>
+      <c r="R45">
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q46">
+        <v>147</v>
+      </c>
+      <c r="P46">
         <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="B47" t="s">
         <v>30</v>
@@ -1838,118 +1938,127 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC47">
-        <v>25</v>
+        <v>148</v>
+      </c>
+      <c r="P47">
+        <v>18</v>
+      </c>
+      <c r="Q47">
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB48">
-        <v>59</v>
-      </c>
-      <c r="AC48">
-        <v>25</v>
+        <v>149</v>
+      </c>
+      <c r="R48">
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC49">
-        <v>25</v>
+        <v>150</v>
+      </c>
+      <c r="N49" t="s">
+        <v>151</v>
+      </c>
+      <c r="P49">
+        <v>18</v>
+      </c>
+      <c r="Q49">
+        <v>17</v>
+      </c>
+      <c r="R49">
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB50">
+        <v>152</v>
+      </c>
+      <c r="Z50">
         <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="AC51">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>126</v>
+      </c>
+      <c r="P52">
+        <v>35</v>
       </c>
       <c r="AB52">
-        <v>30</v>
-      </c>
-      <c r="AC52">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
-      </c>
-      <c r="L53" t="s">
-        <v>109</v>
+        <v>127</v>
+      </c>
+      <c r="Q53">
+        <v>18</v>
       </c>
       <c r="AB53">
         <v>30</v>
@@ -1957,16 +2066,19 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>129</v>
+      </c>
+      <c r="T54">
+        <v>24</v>
       </c>
       <c r="AC54">
         <v>15</v>
@@ -1974,64 +2086,64 @@
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>111</v>
+        <v>130</v>
+      </c>
+      <c r="Q55">
+        <v>35</v>
       </c>
       <c r="AC55">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="P56">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="Q56">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB57">
-        <v>30</v>
-      </c>
-      <c r="AC57">
-        <v>25</v>
+        <v>132</v>
+      </c>
+      <c r="P57">
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B58" t="s">
         <v>31</v>
@@ -2040,27 +2152,27 @@
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC58">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="Q58">
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="P59">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="AC59">
         <v>25</v>
@@ -2068,207 +2180,207 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C60" t="s">
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB60">
+        <v>115</v>
+      </c>
+      <c r="L60" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z60">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C61" t="s">
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>90</v>
-      </c>
-      <c r="P61">
-        <v>18</v>
-      </c>
-      <c r="Q61">
-        <v>17</v>
+        <v>116</v>
+      </c>
+      <c r="AB61">
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
-      </c>
-      <c r="P62">
+        <v>117</v>
+      </c>
+      <c r="Q62">
         <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
-      </c>
-      <c r="L63" t="s">
-        <v>93</v>
-      </c>
-      <c r="P63">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="Q63">
-        <v>37</v>
-      </c>
-      <c r="R63">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="P64">
-        <v>18</v>
-      </c>
-      <c r="Q64">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="S64">
+        <v>12</v>
+      </c>
+      <c r="Y64">
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C65" t="s">
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q65">
+        <v>121</v>
+      </c>
+      <c r="P65">
         <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>79</v>
-      </c>
-      <c r="X66">
-        <v>15</v>
+        <v>122</v>
+      </c>
+      <c r="P66">
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>123</v>
+      </c>
+      <c r="L67" t="s">
+        <v>124</v>
       </c>
       <c r="P67">
         <v>18</v>
       </c>
       <c r="Q67">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
         <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q68">
-        <v>17</v>
-      </c>
-      <c r="AC68">
-        <v>25</v>
+        <v>97</v>
+      </c>
+      <c r="L68" t="s">
+        <v>98</v>
+      </c>
+      <c r="P68">
+        <v>35</v>
+      </c>
+      <c r="AA68">
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>82</v>
-      </c>
-      <c r="P69">
+        <v>99</v>
+      </c>
+      <c r="Q69">
         <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="AC70">
         <v>25</v>
@@ -2276,16 +2388,19 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C71" t="s">
         <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>75</v>
+        <v>102</v>
+      </c>
+      <c r="AB71">
+        <v>59</v>
       </c>
       <c r="AC71">
         <v>25</v>
@@ -2293,24 +2408,24 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
         <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>76</v>
-      </c>
-      <c r="P72">
-        <v>18</v>
+        <v>103</v>
+      </c>
+      <c r="AC72">
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B73" t="s">
         <v>30</v>
@@ -2319,18 +2434,15 @@
         <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="AB73">
-        <v>46</v>
-      </c>
-      <c r="AC73">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B74" t="s">
         <v>26</v>
@@ -2339,10 +2451,7 @@
         <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>61</v>
-      </c>
-      <c r="L74" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="AC74">
         <v>25</v>
@@ -2350,19 +2459,19 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
         <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="AB75">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AC75">
         <v>25</v>
@@ -2370,44 +2479,44 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C76" t="s">
         <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
-      </c>
-      <c r="P76">
-        <v>35</v>
-      </c>
-      <c r="AC76">
-        <v>25</v>
+        <v>108</v>
+      </c>
+      <c r="L76" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB76">
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
         <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AC77">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
         <v>28</v>
@@ -2416,101 +2525,101 @@
         <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA78">
-        <v>15</v>
+        <v>111</v>
+      </c>
+      <c r="AC78">
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
         <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB79">
-        <v>30</v>
+        <v>84</v>
+      </c>
+      <c r="P79">
+        <v>35</v>
+      </c>
+      <c r="Q79">
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C80" t="s">
         <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
-      </c>
-      <c r="L80" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA80">
-        <v>11</v>
+        <v>85</v>
+      </c>
+      <c r="AB80">
+        <v>30</v>
+      </c>
+      <c r="AC80">
+        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C81" t="s">
         <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB81">
-        <v>30</v>
+        <v>86</v>
+      </c>
+      <c r="AC81">
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C82" t="s">
         <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB82">
-        <v>30</v>
+        <v>87</v>
+      </c>
+      <c r="P82">
+        <v>18</v>
+      </c>
+      <c r="AC82">
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C83" t="s">
         <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>51</v>
-      </c>
-      <c r="L83" t="s">
-        <v>52</v>
-      </c>
-      <c r="R83">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="AB83">
         <v>30</v>
@@ -2518,7 +2627,7 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B84" t="s">
         <v>28</v>
@@ -2527,18 +2636,18 @@
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="P84">
-        <v>35</v>
-      </c>
-      <c r="AB84">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="Q84">
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
         <v>31</v>
@@ -2547,184 +2656,178 @@
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q85">
-        <v>35</v>
-      </c>
-      <c r="AB85">
-        <v>30</v>
+        <v>91</v>
+      </c>
+      <c r="P85">
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C86" t="s">
         <v>27</v>
       </c>
       <c r="D86" t="s">
-        <v>55</v>
+        <v>92</v>
+      </c>
+      <c r="L86" t="s">
+        <v>93</v>
       </c>
       <c r="P86">
-        <v>35</v>
-      </c>
-      <c r="AB86">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="Q86">
+        <v>37</v>
+      </c>
+      <c r="R86">
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C87" t="s">
         <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="P87">
+        <v>18</v>
+      </c>
+      <c r="Q87">
         <v>17</v>
-      </c>
-      <c r="Q87">
-        <v>18</v>
-      </c>
-      <c r="R87">
-        <v>17</v>
-      </c>
-      <c r="AC87">
-        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
         <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
-      </c>
-      <c r="R88">
+        <v>95</v>
+      </c>
+      <c r="Q88">
         <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C89" t="s">
         <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
-      </c>
-      <c r="P89">
-        <v>35</v>
-      </c>
-      <c r="R89">
-        <v>35</v>
+        <v>79</v>
+      </c>
+      <c r="X89">
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="B90" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s">
+        <v>80</v>
+      </c>
+      <c r="P90">
+        <v>18</v>
+      </c>
+      <c r="Q90">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A91" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B91" t="s">
         <v>31</v>
       </c>
-      <c r="C90" t="s">
-        <v>27</v>
-      </c>
-      <c r="D90" t="s">
-        <v>47</v>
-      </c>
-      <c r="P90">
-        <v>35</v>
-      </c>
-      <c r="Q90">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>44</v>
-      </c>
-      <c r="B91" t="s">
-        <v>30</v>
-      </c>
       <c r="C91" t="s">
         <v>27</v>
       </c>
       <c r="D91" t="s">
-        <v>48</v>
-      </c>
-      <c r="P91">
-        <v>35</v>
+        <v>81</v>
+      </c>
+      <c r="Q91">
+        <v>17</v>
+      </c>
+      <c r="AC91">
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C92" t="s">
         <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>49</v>
-      </c>
-      <c r="R92">
+        <v>82</v>
+      </c>
+      <c r="P92">
         <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C93" t="s">
         <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>39</v>
-      </c>
-      <c r="P93">
-        <v>35</v>
+        <v>74</v>
+      </c>
+      <c r="AC93">
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C94" t="s">
         <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>40</v>
-      </c>
-      <c r="X94">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="AC94">
         <v>25</v>
@@ -2732,42 +2835,36 @@
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C95" t="s">
         <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="P95">
-        <v>17</v>
-      </c>
-      <c r="AC95">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C96" t="s">
         <v>27</v>
       </c>
       <c r="D96" t="s">
-        <v>42</v>
-      </c>
-      <c r="S96">
-        <v>12</v>
-      </c>
-      <c r="T96">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="AB96">
+        <v>46</v>
       </c>
       <c r="AC96">
         <v>25</v>
@@ -2775,19 +2872,19 @@
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C97" t="s">
         <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>43</v>
-      </c>
-      <c r="S97">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="L97" t="s">
+        <v>62</v>
       </c>
       <c r="AC97">
         <v>25</v>
@@ -2795,22 +2892,19 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C98" t="s">
         <v>27</v>
       </c>
       <c r="D98" t="s">
-        <v>33</v>
-      </c>
-      <c r="L98" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q98">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="AB98">
+        <v>21</v>
       </c>
       <c r="AC98">
         <v>25</v>
@@ -2818,7 +2912,7 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B99" t="s">
         <v>29</v>
@@ -2827,6 +2921,9 @@
         <v>27</v>
       </c>
       <c r="D99" t="s">
+        <v>64</v>
+      </c>
+      <c r="P99">
         <v>35</v>
       </c>
       <c r="AC99">
@@ -2835,35 +2932,480 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C100" t="s">
         <v>27</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y100">
-        <v>30</v>
+        <v>65</v>
+      </c>
+      <c r="AC100">
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
+        <v>66</v>
+      </c>
+      <c r="B101" t="s">
+        <v>28</v>
+      </c>
+      <c r="C101" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA101">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>66</v>
+      </c>
+      <c r="B102" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" t="s">
+        <v>27</v>
+      </c>
+      <c r="D102" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB102">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>66</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="L103" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA103">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>66</v>
+      </c>
+      <c r="B104" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D104" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB104">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>66</v>
+      </c>
+      <c r="B105" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB105">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>50</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106" t="s">
+        <v>51</v>
+      </c>
+      <c r="L106" t="s">
+        <v>52</v>
+      </c>
+      <c r="R106">
+        <v>35</v>
+      </c>
+      <c r="AB106">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>50</v>
+      </c>
+      <c r="B107" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" t="s">
+        <v>27</v>
+      </c>
+      <c r="D107" t="s">
+        <v>53</v>
+      </c>
+      <c r="P107">
+        <v>35</v>
+      </c>
+      <c r="AB107">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>50</v>
+      </c>
+      <c r="B108" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" t="s">
+        <v>27</v>
+      </c>
+      <c r="D108" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q108">
+        <v>35</v>
+      </c>
+      <c r="AB108">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" t="s">
+        <v>27</v>
+      </c>
+      <c r="D109" t="s">
+        <v>55</v>
+      </c>
+      <c r="P109">
+        <v>35</v>
+      </c>
+      <c r="AB109">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>50</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" t="s">
+        <v>27</v>
+      </c>
+      <c r="D110" t="s">
+        <v>56</v>
+      </c>
+      <c r="P110">
+        <v>17</v>
+      </c>
+      <c r="Q110">
+        <v>18</v>
+      </c>
+      <c r="R110">
+        <v>17</v>
+      </c>
+      <c r="AC110">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>44</v>
+      </c>
+      <c r="B111" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D111" t="s">
+        <v>45</v>
+      </c>
+      <c r="R111">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>44</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D112" t="s">
+        <v>46</v>
+      </c>
+      <c r="P112">
+        <v>35</v>
+      </c>
+      <c r="R112">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" t="s">
+        <v>47</v>
+      </c>
+      <c r="P113">
+        <v>35</v>
+      </c>
+      <c r="Q113">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>44</v>
+      </c>
+      <c r="B114" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D114" t="s">
+        <v>48</v>
+      </c>
+      <c r="P114">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="115" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>44</v>
+      </c>
+      <c r="B115" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" t="s">
+        <v>27</v>
+      </c>
+      <c r="D115" t="s">
+        <v>49</v>
+      </c>
+      <c r="R115">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>38</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D116" t="s">
+        <v>39</v>
+      </c>
+      <c r="P116">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="117" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>38</v>
+      </c>
+      <c r="B117" t="s">
+        <v>28</v>
+      </c>
+      <c r="C117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D117" t="s">
+        <v>40</v>
+      </c>
+      <c r="X117">
+        <v>11</v>
+      </c>
+      <c r="AC117">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>38</v>
+      </c>
+      <c r="B118" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D118" t="s">
+        <v>41</v>
+      </c>
+      <c r="P118">
+        <v>17</v>
+      </c>
+      <c r="AC118">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>38</v>
+      </c>
+      <c r="B119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119" t="s">
+        <v>27</v>
+      </c>
+      <c r="D119" t="s">
+        <v>42</v>
+      </c>
+      <c r="S119">
+        <v>12</v>
+      </c>
+      <c r="T119">
+        <v>24</v>
+      </c>
+      <c r="AC119">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>38</v>
+      </c>
+      <c r="B120" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" t="s">
+        <v>27</v>
+      </c>
+      <c r="D120" t="s">
+        <v>43</v>
+      </c>
+      <c r="S120">
+        <v>12</v>
+      </c>
+      <c r="AC120">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
         <v>32</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>27</v>
+      </c>
+      <c r="D121" t="s">
+        <v>33</v>
+      </c>
+      <c r="L121" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q121">
+        <v>35</v>
+      </c>
+      <c r="AC121">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>32</v>
+      </c>
+      <c r="B122" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D122" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC122">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>32</v>
+      </c>
+      <c r="B123" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" t="s">
+        <v>27</v>
+      </c>
+      <c r="D123" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y123">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>32</v>
+      </c>
+      <c r="B124" t="s">
         <v>31</v>
       </c>
-      <c r="C101" t="s">
-        <v>27</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C124" t="s">
+        <v>27</v>
+      </c>
+      <c r="D124" t="s">
         <v>37</v>
       </c>
-      <c r="Q101">
+      <c r="Q124">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31C7293-05B8-42B6-B0EB-1309BD144638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582026E4-9045-48E5-9E76-7CAFB9301D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="283">
   <si>
     <t>업무일자</t>
   </si>
@@ -630,6 +630,258 @@
   </si>
   <si>
     <t>2026-05-04 06:33:20.681726</t>
+  </si>
+  <si>
+    <t>1열 목쿠션 Lite</t>
+  </si>
+  <si>
+    <t>2열 L라인</t>
+  </si>
+  <si>
+    <t>2열 H라인</t>
+  </si>
+  <si>
+    <t>포르쉐 파나메라</t>
+  </si>
+  <si>
+    <t>사각허깅쿠션</t>
+  </si>
+  <si>
+    <t>시트백커버 Lite</t>
+  </si>
+  <si>
+    <t>G70 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>GV70 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>GV70 PE 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>G80 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>GV80(2세대) 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>G80+GV80 콘솔쿠션(3세대)</t>
+  </si>
+  <si>
+    <t>G90 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>팰리(3세대) 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>팰리(LX3) 단문형 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>디올뉴셀토스 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>그랜저 GN7 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>쏘나타 디엣지 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>싼타페 MX5 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>카니발 KA4 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>K8 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>K8 PE 콘솔쿠션 (단문형)</t>
+  </si>
+  <si>
+    <t>K8 PE 콘솔쿠션 (양문형)</t>
+  </si>
+  <si>
+    <t>벤츠 E클래스 W214 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>벤츠 C/E 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>BMW 5시리즈 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>BMW X 시리즈 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>BMW G60 시리즈 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>테슬라 Y 주니퍼 콘솔쿠션</t>
+  </si>
+  <si>
+    <t>G70 시트백커버</t>
+  </si>
+  <si>
+    <t>GV70 PE 시트백커버</t>
+  </si>
+  <si>
+    <t>GV80+G80 시트백커버</t>
+  </si>
+  <si>
+    <t>팰리세이드 시트백커버</t>
+  </si>
+  <si>
+    <t>팰리세이드 LX3 시트백커버</t>
+  </si>
+  <si>
+    <t>그랜저 GN7 시트백커버</t>
+  </si>
+  <si>
+    <t>싼타페 MX5 시트백커버</t>
+  </si>
+  <si>
+    <t>투싼 NX4 시트백커버</t>
+  </si>
+  <si>
+    <t>디올뉴 셀토스 시트백커버</t>
+  </si>
+  <si>
+    <t>쏘나타 시트백커버</t>
+  </si>
+  <si>
+    <t>아반떼 시트백커버</t>
+  </si>
+  <si>
+    <t>카니발 시트백커버</t>
+  </si>
+  <si>
+    <t>쏘렌토 시트백커버</t>
+  </si>
+  <si>
+    <t>K5 시트백커버</t>
+  </si>
+  <si>
+    <t>K8 시트백커버</t>
+  </si>
+  <si>
+    <t>토레스 시트백커버</t>
+  </si>
+  <si>
+    <t>테슬라 시트백커버</t>
+  </si>
+  <si>
+    <t>포르쉐 카이엔</t>
+  </si>
+  <si>
+    <t>캐스퍼</t>
+  </si>
+  <si>
+    <t>테슬라 모델Y</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-18 08:36:55.977048</t>
+  </si>
+  <si>
+    <t>2026-05-18 08:33:36.182454</t>
+  </si>
+  <si>
+    <t>2026-05-18 08:31:07.676755</t>
+  </si>
+  <si>
+    <t>2026-05-18 06:35:00.579732</t>
+  </si>
+  <si>
+    <t>2026-05-18 06:33:02.035518</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-15 08:35:22.260139</t>
+  </si>
+  <si>
+    <t>2026-05-15 06:37:01.899251</t>
+  </si>
+  <si>
+    <t>2026-05-15 06:34:36.726202</t>
+  </si>
+  <si>
+    <t>2026-05-15 06:33:18.781770</t>
+  </si>
+  <si>
+    <t>2026-05-15 03:51:51.073386</t>
+  </si>
+  <si>
+    <t>박정현</t>
+  </si>
+  <si>
+    <t>생산2부-미싱팀</t>
+  </si>
+  <si>
+    <t>2026-05-15 02:09:26.715812</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-14 08:34:18.371994</t>
+  </si>
+  <si>
+    <t>2026-05-14 06:35:33.297666</t>
+  </si>
+  <si>
+    <t>2026-05-14 06:32:26.012684</t>
+  </si>
+  <si>
+    <t>2026-05-14 06:31:26.380690</t>
+  </si>
+  <si>
+    <t>2026-05-14 06:12:30.418860</t>
+  </si>
+  <si>
+    <t>2026-05-14 04:14:29.652860</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-05-13 09:53:36.199467</t>
+  </si>
+  <si>
+    <t>2026-05-13 08:33:07.564209</t>
+  </si>
+  <si>
+    <t>2026-05-13 06:38:51.043510</t>
+  </si>
+  <si>
+    <t>백커버. 하는중...</t>
+  </si>
+  <si>
+    <t>2026-05-13 06:32:23.606873</t>
+  </si>
+  <si>
+    <t>2026-05-13 04:08:56.075150</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-12 23:28:27.418070</t>
+  </si>
+  <si>
+    <t>2026-05-12 08:33:59.272368</t>
+  </si>
+  <si>
+    <t>2026-05-12 08:30:58.760734</t>
+  </si>
+  <si>
+    <t>2026-05-12 06:32:48.556718</t>
+  </si>
+  <si>
+    <t>2026-05-12 06:31:45.234864</t>
   </si>
 </sst>
 </file>
@@ -672,9 +924,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -977,13 +1228,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC124"/>
+  <dimension ref="A1:BZ151"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1071,10 +1319,157 @@
       <c r="AC1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD1" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>203</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>216</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>221</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>222</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>224</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>225</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>227</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>228</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>229</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>230</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>231</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>232</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>233</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>234</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>237</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>238</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>239</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>240</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>241</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>242</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>243</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>244</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>245</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>246</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1083,15 +1478,18 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="P2">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="Y2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -1100,292 +1498,271 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+        <v>250</v>
+      </c>
+      <c r="AC3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q4">
+        <v>35</v>
+      </c>
+      <c r="AC4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q4">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>252</v>
+      </c>
+      <c r="P5">
+        <v>35</v>
+      </c>
+      <c r="AB5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="AC6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q7">
+        <v>35</v>
+      </c>
+      <c r="X7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>256</v>
+      </c>
+      <c r="P8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q9">
         <v>18</v>
       </c>
-      <c r="R4">
+      <c r="R9">
         <v>17</v>
       </c>
-      <c r="Z4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>171</v>
-      </c>
-      <c r="P5">
-        <v>18</v>
-      </c>
-      <c r="AB5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="U9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>172</v>
-      </c>
-      <c r="P6">
-        <v>18</v>
-      </c>
-      <c r="Q6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AC10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC7">
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>264</v>
+      </c>
+      <c r="T13">
+        <v>12</v>
+      </c>
+      <c r="Z13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB14">
+        <v>30</v>
+      </c>
+      <c r="AC14">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>176</v>
-      </c>
-      <c r="L8" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q8">
-        <v>16</v>
-      </c>
-      <c r="AB8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="15" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>178</v>
-      </c>
-      <c r="P9">
-        <v>18</v>
-      </c>
-      <c r="S9">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q10">
-        <v>17</v>
-      </c>
-      <c r="AB10">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB11">
-        <v>30</v>
-      </c>
-      <c r="AC11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>182</v>
-      </c>
-      <c r="P12">
-        <v>17</v>
-      </c>
-      <c r="Q12">
-        <v>18</v>
-      </c>
-      <c r="AB12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB13">
-        <v>30</v>
-      </c>
-      <c r="AC13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+        <v>266</v>
+      </c>
+      <c r="Y15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
-      </c>
-      <c r="L16" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z16">
-        <v>30</v>
+        <v>267</v>
+      </c>
+      <c r="P16">
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>260</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>189</v>
-      </c>
-      <c r="AC17">
-        <v>25</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -1394,13 +1771,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
-      </c>
-      <c r="P18">
-        <v>18</v>
-      </c>
-      <c r="Q18">
-        <v>17</v>
+        <v>269</v>
       </c>
       <c r="AC18">
         <v>25</v>
@@ -1408,172 +1779,178 @@
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>270</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
-      </c>
-      <c r="P19">
-        <v>35</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
-      </c>
-      <c r="L20" t="s">
-        <v>194</v>
-      </c>
-      <c r="P20">
-        <v>35</v>
-      </c>
-      <c r="AB20">
-        <v>30</v>
+        <v>272</v>
+      </c>
+      <c r="Q20">
+        <v>17</v>
+      </c>
+      <c r="AC20">
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z21">
+        <v>273</v>
+      </c>
+      <c r="L21" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB21">
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC22">
-        <v>13</v>
+        <v>275</v>
+      </c>
+      <c r="AB22">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>197</v>
-      </c>
-      <c r="AC23">
-        <v>12</v>
+        <v>276</v>
+      </c>
+      <c r="AB23">
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>192</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
-      </c>
-      <c r="AB24">
-        <v>30</v>
+        <v>278</v>
+      </c>
+      <c r="P24">
+        <v>18</v>
+      </c>
+      <c r="Q24">
+        <v>17</v>
+      </c>
+      <c r="AA24">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB25">
-        <v>30</v>
-      </c>
-      <c r="AC25">
-        <v>15</v>
+        <v>279</v>
+      </c>
+      <c r="P25">
+        <v>18</v>
+      </c>
+      <c r="AA25">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB26">
-        <v>60</v>
+        <v>280</v>
+      </c>
+      <c r="P26">
+        <v>35</v>
+      </c>
+      <c r="Q26">
+        <v>19</v>
+      </c>
+      <c r="R26">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
-      </c>
-      <c r="X27">
-        <v>15</v>
-      </c>
-      <c r="AB27">
+        <v>281</v>
+      </c>
+      <c r="Y27">
         <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -1582,35 +1959,35 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y28">
-        <v>26</v>
-      </c>
-      <c r="AB28">
-        <v>45</v>
+        <v>282</v>
+      </c>
+      <c r="P28">
+        <v>36</v>
+      </c>
+      <c r="Q28">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB29">
-        <v>60</v>
+        <v>168</v>
+      </c>
+      <c r="P29">
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
@@ -1619,18 +1996,15 @@
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>161</v>
-      </c>
-      <c r="U30">
-        <v>30</v>
-      </c>
-      <c r="AC30">
-        <v>20</v>
+        <v>169</v>
+      </c>
+      <c r="Q30">
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
@@ -1639,58 +2013,61 @@
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="L31" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R31">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="Z31">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>164</v>
-      </c>
-      <c r="R32">
-        <v>35</v>
-      </c>
-      <c r="AC32">
-        <v>15</v>
+        <v>171</v>
+      </c>
+      <c r="P32">
+        <v>18</v>
+      </c>
+      <c r="AB32">
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="P33">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q33">
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -1699,18 +2076,15 @@
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q34">
-        <v>18</v>
-      </c>
-      <c r="R34">
-        <v>17</v>
+        <v>174</v>
+      </c>
+      <c r="AC34">
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
@@ -1719,138 +2093,150 @@
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
-      </c>
-      <c r="P35">
+        <v>176</v>
+      </c>
+      <c r="L35" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q35">
+        <v>16</v>
+      </c>
+      <c r="AB35">
         <v>18</v>
-      </c>
-      <c r="Q35">
-        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC36">
-        <v>9</v>
+        <v>178</v>
+      </c>
+      <c r="P36">
+        <v>18</v>
+      </c>
+      <c r="S36">
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37">
-        <v>35</v>
+        <v>180</v>
+      </c>
+      <c r="Q37">
+        <v>17</v>
+      </c>
+      <c r="AB37">
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
-      </c>
-      <c r="R38">
-        <v>53</v>
+        <v>181</v>
+      </c>
+      <c r="AB38">
+        <v>30</v>
+      </c>
+      <c r="AC38">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="P39">
+        <v>17</v>
+      </c>
+      <c r="Q39">
         <v>18</v>
       </c>
-      <c r="Q39">
-        <v>17</v>
+      <c r="AB39">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q40">
-        <v>35</v>
+        <v>183</v>
+      </c>
+      <c r="AB40">
+        <v>30</v>
+      </c>
+      <c r="AC40">
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
-      </c>
-      <c r="P41">
-        <v>35</v>
-      </c>
-      <c r="AC41">
-        <v>16</v>
+        <v>184</v>
+      </c>
+      <c r="AB41">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="R42">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="AC42">
         <v>25</v>
@@ -1858,36 +2244,36 @@
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="P43">
-        <v>35</v>
-      </c>
-      <c r="R43">
-        <v>16</v>
+        <v>187</v>
+      </c>
+      <c r="L43" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z43">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="AC44">
         <v>25</v>
@@ -1895,33 +2281,39 @@
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
-      </c>
-      <c r="R45">
-        <v>35</v>
+        <v>190</v>
+      </c>
+      <c r="P45">
+        <v>18</v>
+      </c>
+      <c r="Q45">
+        <v>17</v>
+      </c>
+      <c r="AC45">
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="P46">
         <v>35</v>
@@ -1929,87 +2321,81 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>193</v>
+      </c>
+      <c r="L47" t="s">
+        <v>194</v>
       </c>
       <c r="P47">
-        <v>18</v>
-      </c>
-      <c r="Q47">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="AB47">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
-      </c>
-      <c r="R48">
-        <v>18</v>
+        <v>195</v>
+      </c>
+      <c r="Z48">
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
-      </c>
-      <c r="N49" t="s">
-        <v>151</v>
-      </c>
-      <c r="P49">
-        <v>18</v>
-      </c>
-      <c r="Q49">
-        <v>17</v>
-      </c>
-      <c r="R49">
-        <v>18</v>
+        <v>196</v>
+      </c>
+      <c r="AC49">
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z50">
-        <v>30</v>
+        <v>197</v>
+      </c>
+      <c r="AC50">
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
         <v>29</v>
@@ -2018,15 +2404,15 @@
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>153</v>
-      </c>
-      <c r="AC51">
-        <v>15</v>
+        <v>198</v>
+      </c>
+      <c r="AB51">
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="B52" t="s">
         <v>30</v>
@@ -2035,58 +2421,55 @@
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
-      </c>
-      <c r="P52">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="AB52">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="AC52">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q53">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="AB53">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
-      </c>
-      <c r="T54">
-        <v>24</v>
-      </c>
-      <c r="AC54">
+        <v>157</v>
+      </c>
+      <c r="X54">
         <v>15</v>
+      </c>
+      <c r="AB54">
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
         <v>31</v>
@@ -2095,18 +2478,18 @@
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q55">
-        <v>35</v>
-      </c>
-      <c r="AC55">
-        <v>15</v>
+        <v>158</v>
+      </c>
+      <c r="Y55">
+        <v>26</v>
+      </c>
+      <c r="AB55">
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="B56" t="s">
         <v>29</v>
@@ -2115,126 +2498,135 @@
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>131</v>
-      </c>
-      <c r="P56">
-        <v>18</v>
-      </c>
-      <c r="Q56">
-        <v>35</v>
+        <v>159</v>
+      </c>
+      <c r="AB56">
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>132</v>
-      </c>
-      <c r="P57">
-        <v>35</v>
+        <v>161</v>
+      </c>
+      <c r="U57">
+        <v>30</v>
+      </c>
+      <c r="AC57">
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C58" t="s">
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>162</v>
+      </c>
+      <c r="L58" t="s">
+        <v>163</v>
       </c>
       <c r="Q58">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="R58">
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>114</v>
-      </c>
-      <c r="P59">
+        <v>164</v>
+      </c>
+      <c r="R59">
         <v>35</v>
       </c>
       <c r="AC59">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>115</v>
-      </c>
-      <c r="L60" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z60">
-        <v>30</v>
+        <v>165</v>
+      </c>
+      <c r="P60">
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB61">
-        <v>60</v>
+        <v>166</v>
+      </c>
+      <c r="Q61">
+        <v>18</v>
+      </c>
+      <c r="R61">
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>117</v>
+        <v>134</v>
+      </c>
+      <c r="P62">
+        <v>18</v>
       </c>
       <c r="Q62">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B63" t="s">
         <v>28</v>
@@ -2243,87 +2635,78 @@
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q63">
-        <v>35</v>
+        <v>135</v>
+      </c>
+      <c r="AC63">
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="P64">
         <v>35</v>
-      </c>
-      <c r="S64">
-        <v>12</v>
-      </c>
-      <c r="Y64">
-        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C65" t="s">
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>121</v>
-      </c>
-      <c r="P65">
-        <v>35</v>
+        <v>137</v>
+      </c>
+      <c r="R65">
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B66" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="P66">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q66">
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
-      </c>
-      <c r="L67" t="s">
-        <v>124</v>
-      </c>
-      <c r="P67">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="Q67">
         <v>35</v>
@@ -2331,64 +2714,67 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
         <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
-      </c>
-      <c r="L68" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="P68">
         <v>35</v>
       </c>
-      <c r="AA68">
-        <v>15</v>
+      <c r="AC68">
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q69">
-        <v>35</v>
+        <v>142</v>
+      </c>
+      <c r="R69">
+        <v>35</v>
+      </c>
+      <c r="AC69">
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC70">
-        <v>25</v>
+        <v>143</v>
+      </c>
+      <c r="P70">
+        <v>35</v>
+      </c>
+      <c r="R70">
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="B71" t="s">
         <v>31</v>
@@ -2397,10 +2783,7 @@
         <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB71">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="AC71">
         <v>25</v>
@@ -2408,7 +2791,7 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="B72" t="s">
         <v>28</v>
@@ -2417,69 +2800,69 @@
         <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC72">
-        <v>25</v>
+        <v>146</v>
+      </c>
+      <c r="R72">
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
         <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB73">
-        <v>30</v>
+        <v>147</v>
+      </c>
+      <c r="P73">
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
         <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC74">
-        <v>25</v>
+        <v>148</v>
+      </c>
+      <c r="P74">
+        <v>18</v>
+      </c>
+      <c r="Q74">
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
         <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB75">
-        <v>30</v>
-      </c>
-      <c r="AC75">
-        <v>25</v>
+        <v>149</v>
+      </c>
+      <c r="R75">
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B76" t="s">
         <v>26</v>
@@ -2488,166 +2871,175 @@
         <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>108</v>
-      </c>
-      <c r="L76" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB76">
-        <v>30</v>
+        <v>150</v>
+      </c>
+      <c r="N76" t="s">
+        <v>151</v>
+      </c>
+      <c r="P76">
+        <v>18</v>
+      </c>
+      <c r="Q76">
+        <v>17</v>
+      </c>
+      <c r="R76">
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
         <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC77">
-        <v>15</v>
+        <v>152</v>
+      </c>
+      <c r="Z77">
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
         <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="AC78">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C79" t="s">
         <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="P79">
         <v>35</v>
       </c>
-      <c r="Q79">
-        <v>18</v>
+      <c r="AB79">
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
         <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>85</v>
+        <v>127</v>
+      </c>
+      <c r="Q80">
+        <v>18</v>
       </c>
       <c r="AB80">
         <v>30</v>
-      </c>
-      <c r="AC80">
-        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C81" t="s">
         <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>86</v>
+        <v>129</v>
+      </c>
+      <c r="T81">
+        <v>24</v>
       </c>
       <c r="AC81">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C82" t="s">
         <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
-      </c>
-      <c r="P82">
-        <v>18</v>
+        <v>130</v>
+      </c>
+      <c r="Q82">
+        <v>35</v>
       </c>
       <c r="AC82">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" t="s">
         <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB83">
-        <v>30</v>
+        <v>131</v>
+      </c>
+      <c r="P83">
+        <v>18</v>
+      </c>
+      <c r="Q83">
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C84" t="s">
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="P84">
-        <v>18</v>
-      </c>
-      <c r="Q84">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B85" t="s">
         <v>31</v>
@@ -2656,135 +3048,129 @@
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
-      </c>
-      <c r="P85">
+        <v>113</v>
+      </c>
+      <c r="Q85">
         <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
         <v>27</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
-      </c>
-      <c r="L86" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="P86">
-        <v>17</v>
-      </c>
-      <c r="Q86">
-        <v>37</v>
-      </c>
-      <c r="R86">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="AC86">
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C87" t="s">
         <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>94</v>
-      </c>
-      <c r="P87">
-        <v>18</v>
-      </c>
-      <c r="Q87">
-        <v>17</v>
+        <v>115</v>
+      </c>
+      <c r="L87" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z87">
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C88" t="s">
         <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q88">
-        <v>35</v>
+        <v>116</v>
+      </c>
+      <c r="AB88">
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
         <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>79</v>
-      </c>
-      <c r="X89">
-        <v>15</v>
+        <v>117</v>
+      </c>
+      <c r="Q89">
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q90">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" t="s">
         <v>29</v>
       </c>
-      <c r="C90" t="s">
-        <v>27</v>
-      </c>
-      <c r="D90" t="s">
-        <v>80</v>
-      </c>
-      <c r="P90">
-        <v>18</v>
-      </c>
-      <c r="Q90">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A91" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B91" t="s">
-        <v>31</v>
-      </c>
       <c r="C91" t="s">
         <v>27</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q91">
-        <v>17</v>
-      </c>
-      <c r="AC91">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P91">
+        <v>35</v>
+      </c>
+      <c r="S91">
+        <v>12</v>
+      </c>
+      <c r="Y91">
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
         <v>30</v>
@@ -2793,7 +3179,7 @@
         <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="P92">
         <v>35</v>
@@ -2801,90 +3187,96 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C93" t="s">
         <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC93">
-        <v>25</v>
+        <v>122</v>
+      </c>
+      <c r="P93">
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C94" t="s">
         <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC94">
-        <v>25</v>
+        <v>123</v>
+      </c>
+      <c r="L94" t="s">
+        <v>124</v>
+      </c>
+      <c r="P94">
+        <v>18</v>
+      </c>
+      <c r="Q94">
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
         <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>76</v>
+        <v>97</v>
+      </c>
+      <c r="L95" t="s">
+        <v>98</v>
       </c>
       <c r="P95">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="AA95">
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
         <v>27</v>
       </c>
       <c r="D96" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB96">
-        <v>46</v>
-      </c>
-      <c r="AC96">
-        <v>25</v>
+        <v>99</v>
+      </c>
+      <c r="Q96">
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C97" t="s">
         <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
-      </c>
-      <c r="L97" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="AC97">
         <v>25</v>
@@ -2892,19 +3284,19 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C98" t="s">
         <v>27</v>
       </c>
       <c r="D98" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="AB98">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="AC98">
         <v>25</v>
@@ -2912,19 +3304,16 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B99" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
         <v>27</v>
       </c>
       <c r="D99" t="s">
-        <v>64</v>
-      </c>
-      <c r="P99">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="AC99">
         <v>25</v>
@@ -2932,41 +3321,41 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C100" t="s">
         <v>27</v>
       </c>
       <c r="D100" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC100">
-        <v>25</v>
+        <v>104</v>
+      </c>
+      <c r="AB100">
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
         <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA101">
-        <v>15</v>
+        <v>105</v>
+      </c>
+      <c r="AC101">
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="B102" t="s">
         <v>29</v>
@@ -2975,15 +3364,18 @@
         <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="AB102">
         <v>30</v>
+      </c>
+      <c r="AC102">
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
@@ -2992,95 +3384,92 @@
         <v>27</v>
       </c>
       <c r="D103" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="L103" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA103">
-        <v>11</v>
+        <v>109</v>
+      </c>
+      <c r="AB103">
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C104" t="s">
         <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB104">
-        <v>30</v>
+        <v>110</v>
+      </c>
+      <c r="AC104">
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B105" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
         <v>27</v>
       </c>
       <c r="D105" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB105">
-        <v>30</v>
+        <v>111</v>
+      </c>
+      <c r="AC105">
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
         <v>27</v>
       </c>
       <c r="D106" t="s">
-        <v>51</v>
-      </c>
-      <c r="L106" t="s">
-        <v>52</v>
-      </c>
-      <c r="R106">
-        <v>35</v>
-      </c>
-      <c r="AB106">
-        <v>30</v>
+        <v>84</v>
+      </c>
+      <c r="P106">
+        <v>35</v>
+      </c>
+      <c r="Q106">
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C107" t="s">
         <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>53</v>
-      </c>
-      <c r="P107">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AB107">
         <v>30</v>
+      </c>
+      <c r="AC107">
+        <v>25</v>
       </c>
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
         <v>31</v>
@@ -3089,64 +3478,52 @@
         <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q108">
-        <v>35</v>
-      </c>
-      <c r="AB108">
-        <v>30</v>
+        <v>86</v>
+      </c>
+      <c r="AC108">
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B109" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C109" t="s">
         <v>27</v>
       </c>
       <c r="D109" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="P109">
-        <v>35</v>
-      </c>
-      <c r="AB109">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="AC109">
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C110" t="s">
         <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>56</v>
-      </c>
-      <c r="P110">
-        <v>17</v>
-      </c>
-      <c r="Q110">
-        <v>18</v>
-      </c>
-      <c r="R110">
-        <v>17</v>
-      </c>
-      <c r="AC110">
+        <v>88</v>
+      </c>
+      <c r="AB110">
         <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B111" t="s">
         <v>28</v>
@@ -3155,55 +3532,61 @@
         <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
-      </c>
-      <c r="R111">
-        <v>35</v>
+        <v>90</v>
+      </c>
+      <c r="P111">
+        <v>18</v>
+      </c>
+      <c r="Q111">
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C112" t="s">
         <v>27</v>
       </c>
       <c r="D112" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="P112">
-        <v>35</v>
-      </c>
-      <c r="R112">
         <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C113" t="s">
         <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>47</v>
+        <v>92</v>
+      </c>
+      <c r="L113" t="s">
+        <v>93</v>
       </c>
       <c r="P113">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="Q113">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="R113">
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B114" t="s">
         <v>30</v>
@@ -3212,15 +3595,18 @@
         <v>27</v>
       </c>
       <c r="D114" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="P114">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q114">
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B115" t="s">
         <v>29</v>
@@ -3229,63 +3615,63 @@
         <v>27</v>
       </c>
       <c r="D115" t="s">
-        <v>49</v>
-      </c>
-      <c r="R115">
+        <v>95</v>
+      </c>
+      <c r="Q115">
         <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B116" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C116" t="s">
         <v>27</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
-      </c>
-      <c r="P116">
-        <v>35</v>
+        <v>79</v>
+      </c>
+      <c r="X116">
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C117" t="s">
         <v>27</v>
       </c>
       <c r="D117" t="s">
-        <v>40</v>
-      </c>
-      <c r="X117">
-        <v>11</v>
-      </c>
-      <c r="AC117">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="P117">
+        <v>18</v>
+      </c>
+      <c r="Q117">
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C118" t="s">
         <v>27</v>
       </c>
       <c r="D118" t="s">
-        <v>41</v>
-      </c>
-      <c r="P118">
+        <v>81</v>
+      </c>
+      <c r="Q118">
         <v>17</v>
       </c>
       <c r="AC118">
@@ -3294,42 +3680,33 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B119" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C119" t="s">
         <v>27</v>
       </c>
       <c r="D119" t="s">
-        <v>42</v>
-      </c>
-      <c r="S119">
-        <v>12</v>
-      </c>
-      <c r="T119">
-        <v>24</v>
-      </c>
-      <c r="AC119">
-        <v>25</v>
+        <v>82</v>
+      </c>
+      <c r="P119">
+        <v>35</v>
       </c>
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B120" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C120" t="s">
         <v>27</v>
       </c>
       <c r="D120" t="s">
-        <v>43</v>
-      </c>
-      <c r="S120">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="AC120">
         <v>25</v>
@@ -3337,22 +3714,16 @@
     </row>
     <row r="121" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B121" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C121" t="s">
         <v>27</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
-      </c>
-      <c r="L121" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q121">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AC121">
         <v>25</v>
@@ -3360,24 +3731,24 @@
     </row>
     <row r="122" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C122" t="s">
         <v>27</v>
       </c>
       <c r="D122" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC122">
-        <v>25</v>
+        <v>76</v>
+      </c>
+      <c r="P122">
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B123" t="s">
         <v>30</v>
@@ -3386,26 +3757,551 @@
         <v>27</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y123">
-        <v>30</v>
+        <v>77</v>
+      </c>
+      <c r="AB123">
+        <v>46</v>
+      </c>
+      <c r="AC123">
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
+        <v>60</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>27</v>
+      </c>
+      <c r="D124" t="s">
+        <v>61</v>
+      </c>
+      <c r="L124" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC124">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>60</v>
+      </c>
+      <c r="B125" t="s">
+        <v>28</v>
+      </c>
+      <c r="C125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D125" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB125">
+        <v>21</v>
+      </c>
+      <c r="AC125">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>60</v>
+      </c>
+      <c r="B126" t="s">
+        <v>29</v>
+      </c>
+      <c r="C126" t="s">
+        <v>27</v>
+      </c>
+      <c r="D126" t="s">
+        <v>64</v>
+      </c>
+      <c r="P126">
+        <v>35</v>
+      </c>
+      <c r="AC126">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>60</v>
+      </c>
+      <c r="B127" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D127" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC127">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>66</v>
+      </c>
+      <c r="B128" t="s">
+        <v>28</v>
+      </c>
+      <c r="C128" t="s">
+        <v>27</v>
+      </c>
+      <c r="D128" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA128">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>66</v>
+      </c>
+      <c r="B129" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D129" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB129">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>66</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="L130" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA130">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>66</v>
+      </c>
+      <c r="B131" t="s">
+        <v>30</v>
+      </c>
+      <c r="C131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D131" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB131">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>66</v>
+      </c>
+      <c r="B132" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" t="s">
+        <v>27</v>
+      </c>
+      <c r="D132" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB132">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D133" t="s">
+        <v>51</v>
+      </c>
+      <c r="L133" t="s">
+        <v>52</v>
+      </c>
+      <c r="R133">
+        <v>35</v>
+      </c>
+      <c r="AB133">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>50</v>
+      </c>
+      <c r="B134" t="s">
+        <v>28</v>
+      </c>
+      <c r="C134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D134" t="s">
+        <v>53</v>
+      </c>
+      <c r="P134">
+        <v>35</v>
+      </c>
+      <c r="AB134">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>50</v>
+      </c>
+      <c r="B135" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q135">
+        <v>35</v>
+      </c>
+      <c r="AB135">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>50</v>
+      </c>
+      <c r="B136" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136" t="s">
+        <v>55</v>
+      </c>
+      <c r="P136">
+        <v>35</v>
+      </c>
+      <c r="AB136">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>50</v>
+      </c>
+      <c r="B137" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" t="s">
+        <v>27</v>
+      </c>
+      <c r="D137" t="s">
+        <v>56</v>
+      </c>
+      <c r="P137">
+        <v>17</v>
+      </c>
+      <c r="Q137">
+        <v>18</v>
+      </c>
+      <c r="R137">
+        <v>17</v>
+      </c>
+      <c r="AC137">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>44</v>
+      </c>
+      <c r="B138" t="s">
+        <v>28</v>
+      </c>
+      <c r="C138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138" t="s">
+        <v>45</v>
+      </c>
+      <c r="R138">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="139" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>44</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D139" t="s">
+        <v>46</v>
+      </c>
+      <c r="P139">
+        <v>35</v>
+      </c>
+      <c r="R139">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="140" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>44</v>
+      </c>
+      <c r="B140" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D140" t="s">
+        <v>47</v>
+      </c>
+      <c r="P140">
+        <v>35</v>
+      </c>
+      <c r="Q140">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="141" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>44</v>
+      </c>
+      <c r="B141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" t="s">
+        <v>48</v>
+      </c>
+      <c r="P141">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="142" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>44</v>
+      </c>
+      <c r="B142" t="s">
+        <v>29</v>
+      </c>
+      <c r="C142" t="s">
+        <v>27</v>
+      </c>
+      <c r="D142" t="s">
+        <v>49</v>
+      </c>
+      <c r="R142">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>38</v>
+      </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143" t="s">
+        <v>39</v>
+      </c>
+      <c r="P143">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="144" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B144" t="s">
+        <v>28</v>
+      </c>
+      <c r="C144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D144" t="s">
+        <v>40</v>
+      </c>
+      <c r="X144">
+        <v>11</v>
+      </c>
+      <c r="AC144">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>38</v>
+      </c>
+      <c r="B145" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" t="s">
+        <v>41</v>
+      </c>
+      <c r="P145">
+        <v>17</v>
+      </c>
+      <c r="AC145">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>38</v>
+      </c>
+      <c r="B146" t="s">
+        <v>29</v>
+      </c>
+      <c r="C146" t="s">
+        <v>27</v>
+      </c>
+      <c r="D146" t="s">
+        <v>42</v>
+      </c>
+      <c r="S146">
+        <v>12</v>
+      </c>
+      <c r="T146">
+        <v>24</v>
+      </c>
+      <c r="AC146">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>38</v>
+      </c>
+      <c r="B147" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" t="s">
+        <v>27</v>
+      </c>
+      <c r="D147" t="s">
+        <v>43</v>
+      </c>
+      <c r="S147">
+        <v>12</v>
+      </c>
+      <c r="AC147">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
         <v>32</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148" t="s">
+        <v>33</v>
+      </c>
+      <c r="L148" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q148">
+        <v>35</v>
+      </c>
+      <c r="AC148">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>32</v>
+      </c>
+      <c r="B149" t="s">
+        <v>29</v>
+      </c>
+      <c r="C149" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC149">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>32</v>
+      </c>
+      <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" t="s">
+        <v>27</v>
+      </c>
+      <c r="D150" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y150">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>32</v>
+      </c>
+      <c r="B151" t="s">
         <v>31</v>
       </c>
-      <c r="C124" t="s">
-        <v>27</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="C151" t="s">
+        <v>27</v>
+      </c>
+      <c r="D151" t="s">
         <v>37</v>
       </c>
-      <c r="Q124">
+      <c r="Q151">
         <v>35</v>
       </c>
     </row>

--- a/worklogs.xlsx
+++ b/worklogs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@업무일지대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582026E4-9045-48E5-9E76-7CAFB9301D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2F31CB-5BE3-4AA9-9409-F16F33DE643C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="306">
   <si>
     <t>업무일자</t>
   </si>
@@ -882,6 +882,75 @@
   </si>
   <si>
     <t>2026-05-12 06:31:45.234864</t>
+  </si>
+  <si>
+    <t>X-콘솔쿠션 (4세대)</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-21 06:37:34.320565</t>
+  </si>
+  <si>
+    <t>2026-05-21 06:36:09.567037</t>
+  </si>
+  <si>
+    <t>2026-05-21 06:35:56.273230</t>
+  </si>
+  <si>
+    <t>2026-05-21 06:35:36.221997</t>
+  </si>
+  <si>
+    <t>장양희</t>
+  </si>
+  <si>
+    <t>2026-05-21 04:12:20.262473</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-20 22:35:29.595658</t>
+  </si>
+  <si>
+    <t>임혜영</t>
+  </si>
+  <si>
+    <t>2026-05-20 08:29:57.063614</t>
+  </si>
+  <si>
+    <t>이선자</t>
+  </si>
+  <si>
+    <t>2026-05-20 08:28:24.159076</t>
+  </si>
+  <si>
+    <t>2026-05-20 06:38:41.672938</t>
+  </si>
+  <si>
+    <t>2026-05-20 06:33:06.539047</t>
+  </si>
+  <si>
+    <t>2026-05-20 06:31:25.393388</t>
+  </si>
+  <si>
+    <t>2026-05-20 04:14:04.572610</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-19 08:33:17.897900</t>
+  </si>
+  <si>
+    <t>2026-05-19 06:35:06.245247</t>
+  </si>
+  <si>
+    <t>2026-05-19 06:32:12.503678</t>
+  </si>
+  <si>
+    <t>2026-05-19 06:31:29.126414</t>
   </si>
 </sst>
 </file>
@@ -1228,10 +1297,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BZ151"/>
+  <dimension ref="A1:CA167"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:78" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1466,10 +1535,13 @@
       <c r="BZ1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="2" spans="1:78" x14ac:dyDescent="0.45">
+      <c r="CA1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:79" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1478,291 +1550,282 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="P2">
-        <v>35</v>
-      </c>
-      <c r="Y2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:78" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+      <c r="Q2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:79" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:78" x14ac:dyDescent="0.45">
+        <v>286</v>
+      </c>
+      <c r="Q3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:79" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q4">
-        <v>35</v>
+        <v>287</v>
       </c>
       <c r="AC4">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:78" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>288</v>
+      </c>
+      <c r="P5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" t="s">
+        <v>290</v>
+      </c>
+      <c r="X6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>292</v>
+      </c>
+      <c r="P7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" t="s">
+        <v>294</v>
+      </c>
+      <c r="AU8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" t="s">
+        <v>296</v>
+      </c>
+      <c r="BS9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>297</v>
+      </c>
+      <c r="P10">
+        <v>35</v>
+      </c>
+      <c r="AB10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>298</v>
+      </c>
+      <c r="X11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>299</v>
+      </c>
+      <c r="AB12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" t="s">
+        <v>261</v>
+      </c>
+      <c r="D13" t="s">
+        <v>300</v>
+      </c>
+      <c r="BY13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
+      </c>
+      <c r="P14">
+        <v>18</v>
+      </c>
+      <c r="Q14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>303</v>
+      </c>
+      <c r="AB15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:79" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>304</v>
+      </c>
+      <c r="P16">
+        <v>17</v>
+      </c>
+      <c r="Q16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>301</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>305</v>
+      </c>
+      <c r="AB17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>248</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>252</v>
-      </c>
-      <c r="P5">
-        <v>35</v>
-      </c>
-      <c r="AB5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>253</v>
-      </c>
-      <c r="AC6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q7">
-        <v>35</v>
-      </c>
-      <c r="X7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>256</v>
-      </c>
-      <c r="P8">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q9">
-        <v>18</v>
-      </c>
-      <c r="R9">
-        <v>17</v>
-      </c>
-      <c r="U9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>258</v>
-      </c>
-      <c r="AC10">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q11">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>254</v>
-      </c>
-      <c r="B12" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" t="s">
-        <v>262</v>
-      </c>
-      <c r="AD12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>264</v>
-      </c>
-      <c r="T13">
-        <v>12</v>
-      </c>
-      <c r="Z13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB14">
-        <v>30</v>
-      </c>
-      <c r="AC14">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>263</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:78" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>267</v>
-      </c>
-      <c r="P16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>263</v>
-      </c>
-      <c r="B17" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" t="s">
-        <v>261</v>
-      </c>
-      <c r="D17" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>263</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -1771,49 +1834,55 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
-      </c>
-      <c r="AC18">
+        <v>249</v>
+      </c>
+      <c r="P18">
+        <v>35</v>
+      </c>
+      <c r="Y18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC19">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>270</v>
-      </c>
-      <c r="B19" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="Q20">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="AC20">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
@@ -1822,18 +1891,18 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>273</v>
-      </c>
-      <c r="L21" t="s">
-        <v>274</v>
+        <v>252</v>
+      </c>
+      <c r="P21">
+        <v>35</v>
       </c>
       <c r="AB21">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
@@ -1842,75 +1911,75 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB22">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.45">
+        <v>253</v>
+      </c>
+      <c r="AC22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>276</v>
-      </c>
-      <c r="AB23">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.45">
+        <v>255</v>
+      </c>
+      <c r="Q23">
+        <v>35</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>256</v>
+      </c>
+      <c r="P24">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" t="s">
-        <v>278</v>
-      </c>
-      <c r="P24">
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q25">
         <v>18</v>
       </c>
-      <c r="Q24">
+      <c r="R25">
         <v>17</v>
       </c>
-      <c r="AA24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>277</v>
-      </c>
-      <c r="B25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" t="s">
-        <v>279</v>
-      </c>
-      <c r="P25">
-        <v>18</v>
-      </c>
-      <c r="AA25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="U25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
@@ -1919,115 +1988,106 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>280</v>
-      </c>
-      <c r="P26">
-        <v>35</v>
-      </c>
-      <c r="Q26">
-        <v>19</v>
-      </c>
-      <c r="R26">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+      <c r="AC26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>281</v>
-      </c>
-      <c r="Y27">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.45">
+        <v>259</v>
+      </c>
+      <c r="Q27">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>282</v>
-      </c>
-      <c r="P28">
-        <v>36</v>
-      </c>
-      <c r="Q28">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.45">
+        <v>262</v>
+      </c>
+      <c r="AD28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>168</v>
-      </c>
-      <c r="P29">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
+        <v>264</v>
+      </c>
+      <c r="T29">
+        <v>12</v>
+      </c>
+      <c r="Z29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q30">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
+        <v>265</v>
+      </c>
+      <c r="AB30">
+        <v>30</v>
+      </c>
+      <c r="AC30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q31">
-        <v>18</v>
-      </c>
-      <c r="R31">
-        <v>17</v>
-      </c>
-      <c r="Z31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
+        <v>266</v>
+      </c>
+      <c r="Y31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s">
         <v>30</v>
@@ -2036,38 +2096,29 @@
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
       <c r="P32">
-        <v>18</v>
-      </c>
-      <c r="AB32">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
-      </c>
-      <c r="P33">
-        <v>18</v>
-      </c>
-      <c r="Q33">
-        <v>17</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -2076,7 +2127,7 @@
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="AC34">
         <v>25</v>
@@ -2084,105 +2135,87 @@
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="D35" t="s">
-        <v>176</v>
-      </c>
-      <c r="L35" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q35">
-        <v>16</v>
-      </c>
-      <c r="AB35">
-        <v>18</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
-      </c>
-      <c r="P36">
-        <v>18</v>
-      </c>
-      <c r="S36">
-        <v>24</v>
+        <v>272</v>
+      </c>
+      <c r="Q36">
+        <v>17</v>
+      </c>
+      <c r="AC36">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>270</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q37">
-        <v>17</v>
+        <v>273</v>
+      </c>
+      <c r="L37" t="s">
+        <v>274</v>
       </c>
       <c r="AB37">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>270</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="AB38">
         <v>30</v>
-      </c>
-      <c r="AC38">
-        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>182</v>
-      </c>
-      <c r="P39">
-        <v>17</v>
-      </c>
-      <c r="Q39">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="AB39">
         <v>30</v>
@@ -2190,7 +2223,7 @@
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
@@ -2199,89 +2232,101 @@
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB40">
-        <v>30</v>
-      </c>
-      <c r="AC40">
-        <v>25</v>
+        <v>278</v>
+      </c>
+      <c r="P40">
+        <v>18</v>
+      </c>
+      <c r="Q40">
+        <v>17</v>
+      </c>
+      <c r="AA40">
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB41">
-        <v>30</v>
+        <v>279</v>
+      </c>
+      <c r="P41">
+        <v>18</v>
+      </c>
+      <c r="AA41">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>277</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC42">
-        <v>25</v>
+        <v>280</v>
+      </c>
+      <c r="P42">
+        <v>35</v>
+      </c>
+      <c r="Q42">
+        <v>19</v>
+      </c>
+      <c r="R42">
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>185</v>
+        <v>277</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>187</v>
-      </c>
-      <c r="L43" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z43">
+        <v>281</v>
+      </c>
+      <c r="Y43">
         <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>277</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>189</v>
-      </c>
-      <c r="AC44">
-        <v>25</v>
+        <v>282</v>
+      </c>
+      <c r="P44">
+        <v>36</v>
+      </c>
+      <c r="Q44">
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s">
         <v>31</v>
@@ -2290,38 +2335,32 @@
         <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="P45">
-        <v>18</v>
-      </c>
-      <c r="Q45">
-        <v>17</v>
-      </c>
-      <c r="AC45">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>191</v>
-      </c>
-      <c r="P46">
+        <v>169</v>
+      </c>
+      <c r="Q46">
         <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
         <v>26</v>
@@ -2330,246 +2369,258 @@
         <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>193</v>
-      </c>
-      <c r="L47" t="s">
-        <v>194</v>
-      </c>
-      <c r="P47">
-        <v>35</v>
-      </c>
-      <c r="AB47">
+        <v>170</v>
+      </c>
+      <c r="Q47">
+        <v>18</v>
+      </c>
+      <c r="R47">
+        <v>17</v>
+      </c>
+      <c r="Z47">
         <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z48">
+        <v>171</v>
+      </c>
+      <c r="P48">
+        <v>18</v>
+      </c>
+      <c r="AB48">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC49">
-        <v>13</v>
+        <v>172</v>
+      </c>
+      <c r="P49">
+        <v>18</v>
+      </c>
+      <c r="Q49">
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="AC50">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>198</v>
+        <v>176</v>
+      </c>
+      <c r="L51" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q51">
+        <v>16</v>
       </c>
       <c r="AB51">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB52">
-        <v>30</v>
-      </c>
-      <c r="AC52">
-        <v>15</v>
+        <v>178</v>
+      </c>
+      <c r="P52">
+        <v>18</v>
+      </c>
+      <c r="S52">
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>180</v>
+      </c>
+      <c r="Q53">
+        <v>17</v>
       </c>
       <c r="AB53">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>157</v>
-      </c>
-      <c r="X54">
-        <v>15</v>
+        <v>181</v>
       </c>
       <c r="AB54">
         <v>30</v>
+      </c>
+      <c r="AC54">
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y55">
-        <v>26</v>
+        <v>182</v>
+      </c>
+      <c r="P55">
+        <v>17</v>
+      </c>
+      <c r="Q55">
+        <v>18</v>
       </c>
       <c r="AB55">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="AB56">
-        <v>60</v>
+        <v>30</v>
+      </c>
+      <c r="AC56">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
-      </c>
-      <c r="U57">
-        <v>30</v>
-      </c>
-      <c r="AC57">
-        <v>20</v>
+        <v>184</v>
+      </c>
+      <c r="AB57">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
-      </c>
-      <c r="L58" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q58">
-        <v>2</v>
-      </c>
-      <c r="R58">
-        <v>28</v>
+        <v>186</v>
+      </c>
+      <c r="AC58">
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>164</v>
-      </c>
-      <c r="R59">
-        <v>35</v>
-      </c>
-      <c r="AC59">
-        <v>15</v>
+        <v>187</v>
+      </c>
+      <c r="L59" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z59">
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B60" t="s">
         <v>30</v>
@@ -2578,15 +2629,15 @@
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
-      </c>
-      <c r="P60">
-        <v>35</v>
+        <v>189</v>
+      </c>
+      <c r="AC60">
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B61" t="s">
         <v>31</v>
@@ -2595,72 +2646,78 @@
         <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>190</v>
+      </c>
+      <c r="P61">
+        <v>18</v>
       </c>
       <c r="Q61">
-        <v>18</v>
-      </c>
-      <c r="R61">
         <v>17</v>
+      </c>
+      <c r="AC61">
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
         <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="P62">
-        <v>18</v>
-      </c>
-      <c r="Q62">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC63">
-        <v>9</v>
+        <v>193</v>
+      </c>
+      <c r="L63" t="s">
+        <v>194</v>
+      </c>
+      <c r="P63">
+        <v>35</v>
+      </c>
+      <c r="AB63">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
-      </c>
-      <c r="P64">
-        <v>35</v>
+        <v>195</v>
+      </c>
+      <c r="Z64">
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="B65" t="s">
         <v>31</v>
@@ -2669,112 +2726,106 @@
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
-      </c>
-      <c r="R65">
-        <v>53</v>
+        <v>196</v>
+      </c>
+      <c r="AC65">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>138</v>
-      </c>
-      <c r="P66">
-        <v>18</v>
-      </c>
-      <c r="Q66">
-        <v>17</v>
+        <v>197</v>
+      </c>
+      <c r="AC66">
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q67">
-        <v>35</v>
+        <v>198</v>
+      </c>
+      <c r="AB67">
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
         <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
-      </c>
-      <c r="P68">
-        <v>35</v>
+        <v>155</v>
+      </c>
+      <c r="AB68">
+        <v>30</v>
       </c>
       <c r="AC68">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>142</v>
-      </c>
-      <c r="R69">
-        <v>35</v>
-      </c>
-      <c r="AC69">
-        <v>25</v>
+        <v>156</v>
+      </c>
+      <c r="AB69">
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>143</v>
-      </c>
-      <c r="P70">
-        <v>35</v>
-      </c>
-      <c r="R70">
-        <v>16</v>
+        <v>157</v>
+      </c>
+      <c r="X70">
+        <v>15</v>
+      </c>
+      <c r="AB70">
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B71" t="s">
         <v>31</v>
@@ -2783,238 +2834,235 @@
         <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC71">
-        <v>25</v>
+        <v>158</v>
+      </c>
+      <c r="Y71">
+        <v>26</v>
+      </c>
+      <c r="AB71">
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
         <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
-      </c>
-      <c r="R72">
-        <v>35</v>
+        <v>159</v>
+      </c>
+      <c r="AB72">
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
         <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>147</v>
-      </c>
-      <c r="P73">
-        <v>35</v>
+        <v>161</v>
+      </c>
+      <c r="U73">
+        <v>30</v>
+      </c>
+      <c r="AC73">
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
         <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>148</v>
-      </c>
-      <c r="P74">
-        <v>18</v>
+        <v>162</v>
+      </c>
+      <c r="L74" t="s">
+        <v>163</v>
       </c>
       <c r="Q74">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="R74">
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
         <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="R75">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="AC75">
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C76" t="s">
         <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>150</v>
-      </c>
-      <c r="N76" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P76">
-        <v>18</v>
-      </c>
-      <c r="Q76">
-        <v>17</v>
-      </c>
-      <c r="R76">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C77" t="s">
         <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z77">
-        <v>30</v>
+        <v>166</v>
+      </c>
+      <c r="Q77">
+        <v>18</v>
+      </c>
+      <c r="R77">
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B78" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C78" t="s">
         <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>153</v>
-      </c>
-      <c r="AC78">
-        <v>15</v>
+        <v>134</v>
+      </c>
+      <c r="P78">
+        <v>18</v>
+      </c>
+      <c r="Q78">
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
         <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
-      </c>
-      <c r="P79">
-        <v>35</v>
-      </c>
-      <c r="AB79">
-        <v>38</v>
+        <v>135</v>
+      </c>
+      <c r="AC79">
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C80" t="s">
         <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q80">
-        <v>18</v>
-      </c>
-      <c r="AB80">
-        <v>30</v>
+        <v>136</v>
+      </c>
+      <c r="P80">
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C81" t="s">
         <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>129</v>
-      </c>
-      <c r="T81">
-        <v>24</v>
-      </c>
-      <c r="AC81">
-        <v>15</v>
+        <v>137</v>
+      </c>
+      <c r="R81">
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
         <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>130</v>
+        <v>138</v>
+      </c>
+      <c r="P82">
+        <v>18</v>
       </c>
       <c r="Q82">
-        <v>35</v>
-      </c>
-      <c r="AC82">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C83" t="s">
         <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
-      </c>
-      <c r="P83">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="Q83">
         <v>35</v>
@@ -3022,269 +3070,275 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="P84">
         <v>35</v>
+      </c>
+      <c r="AC84">
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C85" t="s">
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q85">
-        <v>35</v>
+        <v>142</v>
+      </c>
+      <c r="R85">
+        <v>35</v>
+      </c>
+      <c r="AC85">
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
         <v>27</v>
       </c>
       <c r="D86" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="P86">
         <v>35</v>
       </c>
-      <c r="AC86">
-        <v>25</v>
+      <c r="R86">
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B87" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C87" t="s">
         <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>115</v>
-      </c>
-      <c r="L87" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z87">
-        <v>30</v>
+        <v>144</v>
+      </c>
+      <c r="AC87">
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
         <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB88">
-        <v>60</v>
+        <v>146</v>
+      </c>
+      <c r="R88">
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C89" t="s">
         <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q89">
+        <v>147</v>
+      </c>
+      <c r="P89">
         <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C90" t="s">
         <v>27</v>
       </c>
       <c r="D90" t="s">
-        <v>119</v>
+        <v>148</v>
+      </c>
+      <c r="P90">
+        <v>18</v>
       </c>
       <c r="Q90">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C91" t="s">
         <v>27</v>
       </c>
       <c r="D91" t="s">
-        <v>120</v>
-      </c>
-      <c r="P91">
-        <v>35</v>
-      </c>
-      <c r="S91">
-        <v>12</v>
-      </c>
-      <c r="Y91">
-        <v>16</v>
+        <v>149</v>
+      </c>
+      <c r="R91">
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C92" t="s">
         <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>150</v>
+      </c>
+      <c r="N92" t="s">
+        <v>151</v>
       </c>
       <c r="P92">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="Q92">
+        <v>17</v>
+      </c>
+      <c r="R92">
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C93" t="s">
         <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>122</v>
-      </c>
-      <c r="P93">
-        <v>35</v>
+        <v>152</v>
+      </c>
+      <c r="Z93">
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C94" t="s">
         <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>123</v>
-      </c>
-      <c r="L94" t="s">
-        <v>124</v>
-      </c>
-      <c r="P94">
-        <v>18</v>
-      </c>
-      <c r="Q94">
-        <v>35</v>
+        <v>153</v>
+      </c>
+      <c r="AC94">
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C95" t="s">
         <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>97</v>
-      </c>
-      <c r="L95" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="P95">
         <v>35</v>
       </c>
-      <c r="AA95">
-        <v>15</v>
+      <c r="AB95">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C96" t="s">
         <v>27</v>
       </c>
       <c r="D96" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="Q96">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="AB96">
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C97" t="s">
         <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>100</v>
+        <v>129</v>
+      </c>
+      <c r="T97">
+        <v>24</v>
       </c>
       <c r="AC97">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B98" t="s">
         <v>31</v>
@@ -3293,35 +3347,38 @@
         <v>27</v>
       </c>
       <c r="D98" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB98">
-        <v>59</v>
+        <v>130</v>
+      </c>
+      <c r="Q98">
+        <v>35</v>
       </c>
       <c r="AC98">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C99" t="s">
         <v>27</v>
       </c>
       <c r="D99" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC99">
-        <v>25</v>
+        <v>131</v>
+      </c>
+      <c r="P99">
+        <v>18</v>
+      </c>
+      <c r="Q99">
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B100" t="s">
         <v>30</v>
@@ -3330,44 +3387,44 @@
         <v>27</v>
       </c>
       <c r="D100" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB100">
-        <v>30</v>
+        <v>132</v>
+      </c>
+      <c r="P100">
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
         <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC101">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="Q101">
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C102" t="s">
         <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB102">
-        <v>30</v>
+        <v>114</v>
+      </c>
+      <c r="P102">
+        <v>35</v>
       </c>
       <c r="AC102">
         <v>25</v>
@@ -3375,7 +3432,7 @@
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
@@ -3384,52 +3441,52 @@
         <v>27</v>
       </c>
       <c r="D103" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L103" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB103">
+        <v>98</v>
+      </c>
+      <c r="Z103">
         <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C104" t="s">
         <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC104">
-        <v>15</v>
+        <v>116</v>
+      </c>
+      <c r="AB104">
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C105" t="s">
         <v>27</v>
       </c>
       <c r="D105" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC105">
-        <v>25</v>
+        <v>117</v>
+      </c>
+      <c r="Q105">
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B106" t="s">
         <v>28</v>
@@ -3438,18 +3495,15 @@
         <v>27</v>
       </c>
       <c r="D106" t="s">
-        <v>84</v>
-      </c>
-      <c r="P106">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="Q106">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B107" t="s">
         <v>29</v>
@@ -3458,221 +3512,218 @@
         <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB107">
-        <v>30</v>
-      </c>
-      <c r="AC107">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="P107">
+        <v>35</v>
+      </c>
+      <c r="S107">
+        <v>12</v>
+      </c>
+      <c r="Y107">
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C108" t="s">
         <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC108">
-        <v>25</v>
+        <v>121</v>
+      </c>
+      <c r="P108">
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C109" t="s">
         <v>27</v>
       </c>
       <c r="D109" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="P109">
-        <v>18</v>
-      </c>
-      <c r="AC109">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B110" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C110" t="s">
         <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB110">
-        <v>30</v>
+        <v>123</v>
+      </c>
+      <c r="L110" t="s">
+        <v>124</v>
+      </c>
+      <c r="P110">
+        <v>18</v>
+      </c>
+      <c r="Q110">
+        <v>35</v>
       </c>
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C111" t="s">
         <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>90</v>
+        <v>97</v>
+      </c>
+      <c r="L111" t="s">
+        <v>98</v>
       </c>
       <c r="P111">
-        <v>18</v>
-      </c>
-      <c r="Q111">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="AA111">
+        <v>15</v>
       </c>
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C112" t="s">
         <v>27</v>
       </c>
       <c r="D112" t="s">
-        <v>91</v>
-      </c>
-      <c r="P112">
+        <v>99</v>
+      </c>
+      <c r="Q112">
         <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C113" t="s">
         <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>92</v>
-      </c>
-      <c r="L113" t="s">
-        <v>93</v>
-      </c>
-      <c r="P113">
-        <v>17</v>
-      </c>
-      <c r="Q113">
-        <v>37</v>
-      </c>
-      <c r="R113">
-        <v>18</v>
+        <v>100</v>
+      </c>
+      <c r="AC113">
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C114" t="s">
         <v>27</v>
       </c>
       <c r="D114" t="s">
-        <v>94</v>
-      </c>
-      <c r="P114">
-        <v>18</v>
-      </c>
-      <c r="Q114">
-        <v>17</v>
+        <v>102</v>
+      </c>
+      <c r="AB114">
+        <v>59</v>
+      </c>
+      <c r="AC114">
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C115" t="s">
         <v>27</v>
       </c>
       <c r="D115" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q115">
-        <v>35</v>
+        <v>103</v>
+      </c>
+      <c r="AC115">
+        <v>25</v>
       </c>
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C116" t="s">
         <v>27</v>
       </c>
       <c r="D116" t="s">
-        <v>79</v>
-      </c>
-      <c r="X116">
-        <v>15</v>
+        <v>104</v>
+      </c>
+      <c r="AB116">
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C117" t="s">
         <v>27</v>
       </c>
       <c r="D117" t="s">
-        <v>80</v>
-      </c>
-      <c r="P117">
-        <v>18</v>
-      </c>
-      <c r="Q117">
-        <v>52</v>
+        <v>105</v>
+      </c>
+      <c r="AC117">
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C118" t="s">
         <v>27</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q118">
-        <v>17</v>
+        <v>106</v>
+      </c>
+      <c r="AB118">
+        <v>30</v>
       </c>
       <c r="AC118">
         <v>25</v>
@@ -3680,50 +3731,53 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C119" t="s">
         <v>27</v>
       </c>
       <c r="D119" t="s">
-        <v>82</v>
-      </c>
-      <c r="P119">
-        <v>35</v>
+        <v>108</v>
+      </c>
+      <c r="L119" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB119">
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B120" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C120" t="s">
         <v>27</v>
       </c>
       <c r="D120" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AC120">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C121" t="s">
         <v>27</v>
       </c>
       <c r="D121" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC121">
         <v>25</v>
@@ -3731,36 +3785,39 @@
     </row>
     <row r="122" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B122" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C122" t="s">
         <v>27</v>
       </c>
       <c r="D122" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P122">
+        <v>35</v>
+      </c>
+      <c r="Q122">
         <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C123" t="s">
         <v>27</v>
       </c>
       <c r="D123" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AB123">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AC123">
         <v>25</v>
@@ -3768,19 +3825,16 @@
     </row>
     <row r="124" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C124" t="s">
         <v>27</v>
       </c>
       <c r="D124" t="s">
-        <v>61</v>
-      </c>
-      <c r="L124" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="AC124">
         <v>25</v>
@@ -3788,19 +3842,19 @@
     </row>
     <row r="125" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B125" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C125" t="s">
         <v>27</v>
       </c>
       <c r="D125" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB125">
-        <v>21</v>
+        <v>87</v>
+      </c>
+      <c r="P125">
+        <v>18</v>
       </c>
       <c r="AC125">
         <v>25</v>
@@ -3808,215 +3862,215 @@
     </row>
     <row r="126" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B126" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C126" t="s">
         <v>27</v>
       </c>
       <c r="D126" t="s">
-        <v>64</v>
-      </c>
-      <c r="P126">
-        <v>35</v>
-      </c>
-      <c r="AC126">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="AB126">
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C127" t="s">
         <v>27</v>
       </c>
       <c r="D127" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC127">
-        <v>25</v>
+        <v>90</v>
+      </c>
+      <c r="P127">
+        <v>18</v>
+      </c>
+      <c r="Q127">
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C128" t="s">
         <v>27</v>
       </c>
       <c r="D128" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA128">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="P128">
+        <v>35</v>
       </c>
     </row>
     <row r="129" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C129" t="s">
         <v>27</v>
       </c>
       <c r="D129" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB129">
-        <v>30</v>
+        <v>92</v>
+      </c>
+      <c r="L129" t="s">
+        <v>93</v>
+      </c>
+      <c r="P129">
+        <v>17</v>
+      </c>
+      <c r="Q129">
+        <v>37</v>
+      </c>
+      <c r="R129">
+        <v>18</v>
       </c>
     </row>
     <row r="130" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B130" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C130" t="s">
         <v>27</v>
       </c>
       <c r="D130" t="s">
-        <v>69</v>
-      </c>
-      <c r="L130" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA130">
-        <v>11</v>
+        <v>94</v>
+      </c>
+      <c r="P130">
+        <v>18</v>
+      </c>
+      <c r="Q130">
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C131" t="s">
         <v>27</v>
       </c>
       <c r="D131" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB131">
-        <v>30</v>
+        <v>95</v>
+      </c>
+      <c r="Q131">
+        <v>35</v>
       </c>
     </row>
     <row r="132" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C132" t="s">
         <v>27</v>
       </c>
       <c r="D132" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB132">
-        <v>30</v>
+        <v>79</v>
+      </c>
+      <c r="X132">
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
         <v>27</v>
       </c>
       <c r="D133" t="s">
-        <v>51</v>
-      </c>
-      <c r="L133" t="s">
+        <v>80</v>
+      </c>
+      <c r="P133">
+        <v>18</v>
+      </c>
+      <c r="Q133">
         <v>52</v>
-      </c>
-      <c r="R133">
-        <v>35</v>
-      </c>
-      <c r="AB133">
-        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B134" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C134" t="s">
         <v>27</v>
       </c>
       <c r="D134" t="s">
-        <v>53</v>
-      </c>
-      <c r="P134">
-        <v>35</v>
-      </c>
-      <c r="AB134">
-        <v>30</v>
+        <v>81</v>
+      </c>
+      <c r="Q134">
+        <v>17</v>
+      </c>
+      <c r="AC134">
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B135" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C135" t="s">
         <v>27</v>
       </c>
       <c r="D135" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q135">
-        <v>35</v>
-      </c>
-      <c r="AB135">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="P135">
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B136" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C136" t="s">
         <v>27</v>
       </c>
       <c r="D136" t="s">
-        <v>55</v>
-      </c>
-      <c r="P136">
-        <v>35</v>
-      </c>
-      <c r="AB136">
-        <v>30</v>
+        <v>74</v>
+      </c>
+      <c r="AC136">
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B137" t="s">
         <v>29</v>
@@ -4025,98 +4079,92 @@
         <v>27</v>
       </c>
       <c r="D137" t="s">
-        <v>56</v>
-      </c>
-      <c r="P137">
-        <v>17</v>
-      </c>
-      <c r="Q137">
-        <v>18</v>
-      </c>
-      <c r="R137">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="AC137">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B138" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C138" t="s">
         <v>27</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
-      </c>
-      <c r="R138">
-        <v>35</v>
+        <v>76</v>
+      </c>
+      <c r="P138">
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B139" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C139" t="s">
         <v>27</v>
       </c>
       <c r="D139" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB139">
         <v>46</v>
       </c>
-      <c r="P139">
-        <v>35</v>
-      </c>
-      <c r="R139">
-        <v>35</v>
+      <c r="AC139">
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B140" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C140" t="s">
         <v>27</v>
       </c>
       <c r="D140" t="s">
-        <v>47</v>
-      </c>
-      <c r="P140">
-        <v>35</v>
-      </c>
-      <c r="Q140">
-        <v>35</v>
+        <v>61</v>
+      </c>
+      <c r="L140" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC140">
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C141" t="s">
         <v>27</v>
       </c>
       <c r="D141" t="s">
-        <v>48</v>
-      </c>
-      <c r="P141">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="AB141">
+        <v>21</v>
+      </c>
+      <c r="AC141">
+        <v>25</v>
       </c>
     </row>
     <row r="142" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B142" t="s">
         <v>29</v>
@@ -4125,32 +4173,35 @@
         <v>27</v>
       </c>
       <c r="D142" t="s">
-        <v>49</v>
-      </c>
-      <c r="R142">
-        <v>35</v>
+        <v>64</v>
+      </c>
+      <c r="P142">
+        <v>35</v>
+      </c>
+      <c r="AC142">
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B143" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C143" t="s">
         <v>27</v>
       </c>
       <c r="D143" t="s">
-        <v>39</v>
-      </c>
-      <c r="P143">
-        <v>35</v>
+        <v>65</v>
+      </c>
+      <c r="AC143">
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B144" t="s">
         <v>28</v>
@@ -4159,138 +4210,129 @@
         <v>27</v>
       </c>
       <c r="D144" t="s">
-        <v>40</v>
-      </c>
-      <c r="X144">
-        <v>11</v>
-      </c>
-      <c r="AC144">
-        <v>25</v>
+        <v>67</v>
+      </c>
+      <c r="AA144">
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C145" t="s">
         <v>27</v>
       </c>
       <c r="D145" t="s">
-        <v>41</v>
-      </c>
-      <c r="P145">
-        <v>17</v>
-      </c>
-      <c r="AC145">
-        <v>25</v>
+        <v>68</v>
+      </c>
+      <c r="AB145">
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C146" t="s">
         <v>27</v>
       </c>
       <c r="D146" t="s">
-        <v>42</v>
-      </c>
-      <c r="S146">
-        <v>12</v>
-      </c>
-      <c r="T146">
-        <v>24</v>
-      </c>
-      <c r="AC146">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="L146" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA146">
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C147" t="s">
         <v>27</v>
       </c>
       <c r="D147" t="s">
-        <v>43</v>
-      </c>
-      <c r="S147">
-        <v>12</v>
-      </c>
-      <c r="AC147">
-        <v>25</v>
+        <v>71</v>
+      </c>
+      <c r="AB147">
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C148" t="s">
         <v>27</v>
       </c>
       <c r="D148" t="s">
-        <v>33</v>
-      </c>
-      <c r="L148" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q148">
-        <v>35</v>
-      </c>
-      <c r="AC148">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="AB148">
+        <v>30</v>
       </c>
     </row>
     <row r="149" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B149" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C149" t="s">
         <v>27</v>
       </c>
       <c r="D149" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC149">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="L149" t="s">
+        <v>52</v>
+      </c>
+      <c r="R149">
+        <v>35</v>
+      </c>
+      <c r="AB149">
+        <v>30</v>
       </c>
     </row>
     <row r="150" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B150" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C150" t="s">
         <v>27</v>
       </c>
       <c r="D150" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y150">
+        <v>53</v>
+      </c>
+      <c r="P150">
+        <v>35</v>
+      </c>
+      <c r="AB150">
         <v>30</v>
       </c>
     </row>
     <row r="151" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B151" t="s">
         <v>31</v>
@@ -4299,9 +4341,323 @@
         <v>27</v>
       </c>
       <c r="D151" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q151">
+        <v>35</v>
+      </c>
+      <c r="AB151">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>50</v>
+      </c>
+      <c r="B152" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" t="s">
+        <v>27</v>
+      </c>
+      <c r="D152" t="s">
+        <v>55</v>
+      </c>
+      <c r="P152">
+        <v>35</v>
+      </c>
+      <c r="AB152">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>50</v>
+      </c>
+      <c r="B153" t="s">
+        <v>29</v>
+      </c>
+      <c r="C153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" t="s">
+        <v>56</v>
+      </c>
+      <c r="P153">
+        <v>17</v>
+      </c>
+      <c r="Q153">
+        <v>18</v>
+      </c>
+      <c r="R153">
+        <v>17</v>
+      </c>
+      <c r="AC153">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>44</v>
+      </c>
+      <c r="B154" t="s">
+        <v>28</v>
+      </c>
+      <c r="C154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D154" t="s">
+        <v>45</v>
+      </c>
+      <c r="R154">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="155" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>44</v>
+      </c>
+      <c r="B155" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="P155">
+        <v>35</v>
+      </c>
+      <c r="R155">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="156" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>44</v>
+      </c>
+      <c r="B156" t="s">
+        <v>31</v>
+      </c>
+      <c r="C156" t="s">
+        <v>27</v>
+      </c>
+      <c r="D156" t="s">
+        <v>47</v>
+      </c>
+      <c r="P156">
+        <v>35</v>
+      </c>
+      <c r="Q156">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="157" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>44</v>
+      </c>
+      <c r="B157" t="s">
+        <v>30</v>
+      </c>
+      <c r="C157" t="s">
+        <v>27</v>
+      </c>
+      <c r="D157" t="s">
+        <v>48</v>
+      </c>
+      <c r="P157">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="158" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>44</v>
+      </c>
+      <c r="B158" t="s">
+        <v>29</v>
+      </c>
+      <c r="C158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158" t="s">
+        <v>49</v>
+      </c>
+      <c r="R158">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="159" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D159" t="s">
+        <v>39</v>
+      </c>
+      <c r="P159">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="160" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>38</v>
+      </c>
+      <c r="B160" t="s">
+        <v>28</v>
+      </c>
+      <c r="C160" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160" t="s">
+        <v>40</v>
+      </c>
+      <c r="X160">
+        <v>11</v>
+      </c>
+      <c r="AC160">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>38</v>
+      </c>
+      <c r="B161" t="s">
+        <v>30</v>
+      </c>
+      <c r="C161" t="s">
+        <v>27</v>
+      </c>
+      <c r="D161" t="s">
+        <v>41</v>
+      </c>
+      <c r="P161">
+        <v>17</v>
+      </c>
+      <c r="AC161">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>38</v>
+      </c>
+      <c r="B162" t="s">
+        <v>29</v>
+      </c>
+      <c r="C162" t="s">
+        <v>27</v>
+      </c>
+      <c r="D162" t="s">
+        <v>42</v>
+      </c>
+      <c r="S162">
+        <v>12</v>
+      </c>
+      <c r="T162">
+        <v>24</v>
+      </c>
+      <c r="AC162">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>38</v>
+      </c>
+      <c r="B163" t="s">
+        <v>31</v>
+      </c>
+      <c r="C163" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163" t="s">
+        <v>43</v>
+      </c>
+      <c r="S163">
+        <v>12</v>
+      </c>
+      <c r="AC163">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>32</v>
+      </c>
+      <c r="B164" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" t="s">
+        <v>27</v>
+      </c>
+      <c r="D164" t="s">
+        <v>33</v>
+      </c>
+      <c r="L164" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q164">
+        <v>35</v>
+      </c>
+      <c r="AC164">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>32</v>
+      </c>
+      <c r="B165" t="s">
+        <v>29</v>
+      </c>
+      <c r="C165" t="s">
+        <v>27</v>
+      </c>
+      <c r="D165" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC165">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>32</v>
+      </c>
+      <c r="B166" t="s">
+        <v>30</v>
+      </c>
+      <c r="C166" t="s">
+        <v>27</v>
+      </c>
+      <c r="D166" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y166">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>32</v>
+      </c>
+      <c r="B167" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" t="s">
+        <v>27</v>
+      </c>
+      <c r="D167" t="s">
         <v>37</v>
       </c>
-      <c r="Q151">
+      <c r="Q167">
         <v>35</v>
       </c>
     </row>
